--- a/data/processed/idc_data.xlsx
+++ b/data/processed/idc_data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -847,13 +847,13 @@
         <v>0.2272727272727273</v>
       </c>
       <c r="C37" t="n">
-        <v>0.05882352941176449</v>
+        <v>0.0588235294117644</v>
       </c>
       <c r="D37" t="n">
         <v>0.8309695443551434</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3723552670132118</v>
+        <v>0.3723552670132117</v>
       </c>
     </row>
     <row r="38">
@@ -866,7 +866,7 @@
         <v>0.1818181818181812</v>
       </c>
       <c r="C38" t="n">
-        <v>0.05882352941176449</v>
+        <v>0.0588235294117644</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -885,7 +885,7 @@
         <v>0.1818181818181812</v>
       </c>
       <c r="C39" t="n">
-        <v>0.05882352941176449</v>
+        <v>0.0588235294117644</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0.2727272727272735</v>
       </c>
       <c r="C41" t="n">
-        <v>0.05882352941176449</v>
+        <v>0.0588235294117644</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.318181818181818</v>
+        <v>0.3181818181818179</v>
       </c>
       <c r="C42" t="n">
         <v>0.1176470588235295</v>
@@ -948,7 +948,7 @@
         <v>0.8324983307105308</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4227757359052928</v>
+        <v>0.4227757359052927</v>
       </c>
     </row>
     <row r="43">
@@ -999,7 +999,7 @@
         <v>0.2727272727272735</v>
       </c>
       <c r="C45" t="n">
-        <v>0.05882352941176449</v>
+        <v>0.0588235294117644</v>
       </c>
       <c r="D45" t="n">
         <v>0.7830522467498834</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4090909090909086</v>
+        <v>0.4090909090909085</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4546540657780138</v>
+        <v>0.4546540657780137</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4242786279866109</v>
+        <v>0.4242786279866108</v>
       </c>
     </row>
     <row r="49">
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9545454545454555</v>
+        <v>0.9545454545454556</v>
       </c>
       <c r="C51" t="n">
-        <v>0.04999999999999982</v>
+        <v>0.0499999999999998</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9191340608899673</v>
+        <v>0.9191340608899672</v>
       </c>
       <c r="E51" t="n">
         <v>0.6412265051451409</v>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9545454545454555</v>
+        <v>0.9545454545454556</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="D52" t="n">
         <v>0.9354739862101402</v>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9545454545454555</v>
+        <v>0.9545454545454556</v>
       </c>
       <c r="C53" t="n">
-        <v>0.04999999999999982</v>
+        <v>0.0499999999999998</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9759592328097707</v>
+        <v>0.9759592328097708</v>
       </c>
       <c r="E53" t="n">
         <v>0.6601682291184087</v>
@@ -1170,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="D54" t="n">
         <v>0.8883007681125101</v>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4400000000000006</v>
+        <v>0.4400000000000005</v>
       </c>
       <c r="C60" t="n">
         <v>0.5</v>
@@ -1325,7 +1325,7 @@
         <v>0.5</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9725506805246665</v>
+        <v>0.9725506805246664</v>
       </c>
       <c r="E62" t="n">
         <v>0.6908502268415555</v>
@@ -1363,7 +1363,7 @@
         <v>0.5499999999999998</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9749943209794701</v>
+        <v>0.97499432097947</v>
       </c>
       <c r="E64" t="n">
         <v>0.7349981069931566</v>
@@ -1382,7 +1382,7 @@
         <v>0.5</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9310890047696613</v>
+        <v>0.9310890047696612</v>
       </c>
       <c r="E65" t="n">
         <v>0.7170296682565538</v>
@@ -1499,7 +1499,7 @@
         <v>0.1978798745881518</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3326266248627173</v>
+        <v>0.3326266248627172</v>
       </c>
     </row>
     <row r="72">
@@ -1556,7 +1556,7 @@
         <v>0.3628231483643701</v>
       </c>
       <c r="E74" t="n">
-        <v>0.33094104945479</v>
+        <v>0.3309410494547899</v>
       </c>
     </row>
     <row r="75">
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.1200000000000003</v>
+        <v>0.1200000000000002</v>
       </c>
       <c r="C75" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4356421767454646</v>
+        <v>0.4356421767454645</v>
       </c>
       <c r="E75" t="n">
         <v>0.2852140589151549</v>
@@ -1629,10 +1629,10 @@
         <v>0.25</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2399283557599176</v>
+        <v>0.2399283557599175</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2003464889570097</v>
+        <v>0.2003464889570096</v>
       </c>
     </row>
     <row r="79">
@@ -1648,7 +1648,7 @@
         <v>0.25</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1629527256875273</v>
+        <v>0.1629527256875272</v>
       </c>
       <c r="E79" t="n">
         <v>0.2117249826365829</v>
@@ -1670,7 +1670,7 @@
         <v>0.1102481552651509</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2021814838538158</v>
+        <v>0.2021814838538157</v>
       </c>
     </row>
     <row r="81">
@@ -1702,7 +1702,7 @@
         <v>0.1111111111111114</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.03703703703703626</v>
+        <v>0.0370370370370362</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01234567901234542</v>
+        <v>0.0123456790123454</v>
       </c>
     </row>
     <row r="84">
@@ -1743,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.07217268456268752</v>
+        <v>0.07217268456268749</v>
       </c>
       <c r="E84" t="n">
-        <v>0.02405756152089584</v>
+        <v>0.0240575615208958</v>
       </c>
     </row>
     <row r="85">
@@ -1765,7 +1765,7 @@
         <v>0.2373397296057668</v>
       </c>
       <c r="E85" t="n">
-        <v>0.07911324320192227</v>
+        <v>0.0791132432019222</v>
       </c>
     </row>
     <row r="86">
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.03571428571428621</v>
+        <v>0.0357142857142862</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1736702105847082</v>
+        <v>0.1736702105847081</v>
       </c>
       <c r="E86" t="n">
-        <v>0.06979483209966479</v>
+        <v>0.06979483209966469</v>
       </c>
     </row>
     <row r="87">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.1428571428571436</v>
+        <v>0.1428571428571435</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1512087838932729</v>
+        <v>0.1512087838932728</v>
       </c>
       <c r="E88" t="n">
         <v>0.1337362612977575</v>
@@ -1838,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.175105132324621</v>
+        <v>0.1751051323246209</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1655112345843977</v>
+        <v>0.1655112345843976</v>
       </c>
     </row>
     <row r="90">
@@ -1854,13 +1854,13 @@
         <v>0.2142857142857147</v>
       </c>
       <c r="C90" t="n">
-        <v>0.04347826086956506</v>
+        <v>0.043478260869565</v>
       </c>
       <c r="D90" t="n">
-        <v>0.09045990357805485</v>
+        <v>0.09045990357805481</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1160746262444449</v>
+        <v>0.1160746262444448</v>
       </c>
     </row>
     <row r="91">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1071428571428574</v>
+        <v>0.1071428571428573</v>
       </c>
       <c r="C91" t="n">
-        <v>0.04347826086956506</v>
+        <v>0.043478260869565</v>
       </c>
       <c r="D91" t="n">
-        <v>0.03831298161070876</v>
+        <v>0.0383129816107087</v>
       </c>
       <c r="E91" t="n">
-        <v>0.06297803320771041</v>
+        <v>0.06297803320771039</v>
       </c>
     </row>
     <row r="92">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.1428571428571436</v>
+        <v>0.1428571428571435</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.01791067967242742</v>
+        <v>0.0179106796724274</v>
       </c>
       <c r="E92" t="n">
-        <v>0.05358927417652367</v>
+        <v>0.0535892741765236</v>
       </c>
     </row>
     <row r="93">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.1071428571428574</v>
+        <v>0.1071428571428573</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.04898742351801629</v>
+        <v>0.0489874235180162</v>
       </c>
       <c r="E93" t="n">
-        <v>0.05204342688695789</v>
+        <v>0.0520434268869578</v>
       </c>
     </row>
     <row r="94">
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0.006163490244665353</v>
+        <v>0.0061634902446653</v>
       </c>
       <c r="E94" t="n">
-        <v>0.06157830627203129</v>
+        <v>0.0615783062720312</v>
       </c>
     </row>
     <row r="95">
@@ -1971,10 +1971,10 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1239804710481171</v>
+        <v>0.123980471048117</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1484696808255631</v>
+        <v>0.148469680825563</v>
       </c>
     </row>
     <row r="97">
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2448778821631855</v>
+        <v>0.2448778821631854</v>
       </c>
       <c r="E97" t="n">
         <v>0.2125783416734429</v>
@@ -2012,7 +2012,7 @@
         <v>0.2320166827458945</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2082912752010126</v>
+        <v>0.2082912752010125</v>
       </c>
     </row>
     <row r="99">
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2854673416493079</v>
+        <v>0.2854673416493078</v>
       </c>
       <c r="E99" t="n">
         <v>0.2856319710259599</v>
@@ -2044,13 +2044,13 @@
         <v>0.6785714285714292</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03999999999999986</v>
+        <v>0.0399999999999998</v>
       </c>
       <c r="D100" t="n">
         <v>0.2905293572727042</v>
       </c>
       <c r="E100" t="n">
-        <v>0.3363669286147111</v>
+        <v>0.336366928614711</v>
       </c>
     </row>
     <row r="101">
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0.03999999999999986</v>
+        <v>0.0399999999999998</v>
       </c>
       <c r="D101" t="n">
         <v>0.3513175817075109</v>
@@ -2082,7 +2082,7 @@
         <v>0.8999999999999998</v>
       </c>
       <c r="C102" t="n">
-        <v>0.03999999999999986</v>
+        <v>0.0399999999999998</v>
       </c>
       <c r="D102" t="n">
         <v>0.2860368403049701</v>
@@ -2101,7 +2101,7 @@
         <v>0.9333333333333336</v>
       </c>
       <c r="C103" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.08</v>
       </c>
       <c r="D103" t="n">
         <v>0.2805459391879865</v>
@@ -2123,7 +2123,7 @@
         <v>0.1199999999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2809435606936265</v>
+        <v>0.2809435606936264</v>
       </c>
       <c r="E104" t="n">
         <v>0.3558700757867643</v>
@@ -2164,7 +2164,7 @@
         <v>0.1981927225528276</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2393975741842758</v>
+        <v>0.2393975741842757</v>
       </c>
     </row>
     <row r="107">
@@ -2180,10 +2180,10 @@
         <v>0.1199999999999999</v>
       </c>
       <c r="D107" t="n">
-        <v>0.02479784971327119</v>
+        <v>0.0247978497132711</v>
       </c>
       <c r="E107" t="n">
-        <v>0.1371548387933127</v>
+        <v>0.1371548387933126</v>
       </c>
     </row>
     <row r="108">
@@ -2196,7 +2196,7 @@
         <v>0.2666666666666669</v>
       </c>
       <c r="C108" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.08</v>
       </c>
       <c r="D108" t="n">
         <v>0.1035980211576326</v>
@@ -2215,10 +2215,10 @@
         <v>0.2333333333333331</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1599999999999998</v>
+        <v>0.1599999999999997</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2048299465559415</v>
+        <v>0.2048299465559414</v>
       </c>
       <c r="E109" t="n">
         <v>0.1993877599630914</v>
@@ -2253,13 +2253,13 @@
         <v>0.3999999999999997</v>
       </c>
       <c r="C111" t="n">
-        <v>0.32</v>
+        <v>0.3199999999999999</v>
       </c>
       <c r="D111" t="n">
         <v>0.4283229775251577</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3827743258417192</v>
+        <v>0.3827743258417191</v>
       </c>
     </row>
     <row r="112">
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3599999999999998</v>
+        <v>0.3599999999999997</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3165758112709071</v>
+        <v>0.316575811270907</v>
       </c>
       <c r="E112" t="n">
         <v>0.2255252704236356</v>
@@ -2291,13 +2291,13 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2399999999999999</v>
+        <v>0.2399999999999998</v>
       </c>
       <c r="D113" t="n">
         <v>0.1678060787477241</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1359353595825747</v>
+        <v>0.1359353595825746</v>
       </c>
     </row>
     <row r="114">
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1599999999999998</v>
+        <v>0.1599999999999997</v>
       </c>
       <c r="D114" t="n">
-        <v>0.01685373950402727</v>
+        <v>0.0168537395040272</v>
       </c>
       <c r="E114" t="n">
-        <v>0.05895124650134235</v>
+        <v>0.0589512465013423</v>
       </c>
     </row>
     <row r="115">
@@ -2329,13 +2329,13 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.08</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02666666666666669</v>
+        <v>0.0266666666666666</v>
       </c>
     </row>
     <row r="116">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.05882352941176417</v>
+        <v>0.0588235294117641</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>0.01960784313725472</v>
+        <v>0.0196078431372547</v>
       </c>
     </row>
     <row r="117">
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0.05882352941176464</v>
+        <v>0.0588235294117646</v>
       </c>
     </row>
     <row r="118">
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.1568627450980391</v>
       </c>
     </row>
     <row r="120">
@@ -2468,7 +2468,7 @@
         <v>0.2153533575103212</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2482550407387346</v>
+        <v>0.2482550407387345</v>
       </c>
     </row>
     <row r="123">
@@ -2500,7 +2500,7 @@
         <v>0.6078431372549018</v>
       </c>
       <c r="C124" t="n">
-        <v>0.03124999999999989</v>
+        <v>0.0312499999999998</v>
       </c>
       <c r="D124" t="n">
         <v>0.2545599775084994</v>
@@ -2525,7 +2525,7 @@
         <v>0.2814720600383868</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3029743468101813</v>
+        <v>0.3029743468101812</v>
       </c>
     </row>
     <row r="126">
@@ -2538,7 +2538,7 @@
         <v>0.7058823529411763</v>
       </c>
       <c r="C126" t="n">
-        <v>0.03124999999999989</v>
+        <v>0.0312499999999998</v>
       </c>
       <c r="D126" t="n">
         <v>0.2878714351788128</v>
@@ -2557,7 +2557,7 @@
         <v>0.7843137254901964</v>
       </c>
       <c r="C127" t="n">
-        <v>0.03124999999999989</v>
+        <v>0.0312499999999998</v>
       </c>
       <c r="D127" t="n">
         <v>0.3567797887508668</v>
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.9607843137254903</v>
+        <v>0.9607843137254904</v>
       </c>
       <c r="C128" t="n">
-        <v>0.06250000000000006</v>
+        <v>0.0625</v>
       </c>
       <c r="D128" t="n">
         <v>0.4338893293994195</v>
       </c>
       <c r="E128" t="n">
-        <v>0.4857245477083033</v>
+        <v>0.4857245477083032</v>
       </c>
     </row>
     <row r="129">
@@ -2595,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>0.06250000000000006</v>
+        <v>0.0625</v>
       </c>
       <c r="D129" t="n">
         <v>0.5109885971651589</v>
@@ -2614,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0.09374999999999994</v>
+        <v>0.0937499999999999</v>
       </c>
       <c r="D130" t="n">
         <v>0.5224447035496396</v>
@@ -2671,7 +2671,7 @@
         <v>0.9242424242424242</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2187500000000001</v>
+        <v>0.21875</v>
       </c>
       <c r="D133" t="n">
         <v>0.7999634422509253</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.9545454545454545</v>
+        <v>0.9545454545454544</v>
       </c>
       <c r="C137" t="n">
-        <v>0.3750000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="D137" t="n">
         <v>0.8621984129111688</v>
@@ -2826,7 +2826,7 @@
         <v>0.5624999999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9434585701441283</v>
+        <v>0.9434585701441284</v>
       </c>
       <c r="E141" t="n">
         <v>0.8353195233813761</v>
@@ -2845,7 +2845,7 @@
         <v>0.5624999999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9341003903548799</v>
+        <v>0.93410039035488</v>
       </c>
       <c r="E142" t="n">
         <v>0.8322001301182933</v>
@@ -2883,7 +2883,7 @@
         <v>0.6562499999999999</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9359548364085427</v>
+        <v>0.9359548364085428</v>
       </c>
       <c r="E144" t="n">
         <v>0.8640682788028475</v>
@@ -2921,7 +2921,7 @@
         <v>0.6562499999999999</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9534504164253911</v>
+        <v>0.9534504164253912</v>
       </c>
       <c r="E146" t="n">
         <v>0.8699001388084637</v>
@@ -2962,7 +2962,7 @@
         <v>0.987505664722233</v>
       </c>
       <c r="E148" t="n">
-        <v>0.9020852215740777</v>
+        <v>0.9020852215740776</v>
       </c>
     </row>
     <row r="149">
@@ -3016,7 +3016,7 @@
         <v>0.6562499999999999</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9045886593715887</v>
+        <v>0.9045886593715888</v>
       </c>
       <c r="E151" t="n">
         <v>0.8094361796298871</v>
@@ -3168,7 +3168,7 @@
         <v>0.46875</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9710731241272009</v>
+        <v>0.9710731241272008</v>
       </c>
       <c r="E159" t="n">
         <v>0.7369691538255329</v>
@@ -3187,7 +3187,7 @@
         <v>0.46875</v>
       </c>
       <c r="D160" t="n">
-        <v>0.9526198528080617</v>
+        <v>0.9526198528080616</v>
       </c>
       <c r="E160" t="n">
         <v>0.7308180633858198</v>
@@ -3206,7 +3206,7 @@
         <v>0.4375000000000001</v>
       </c>
       <c r="D161" t="n">
-        <v>0.9347747781531663</v>
+        <v>0.9347747781531665</v>
       </c>
       <c r="E161" t="n">
         <v>0.7265012312719391</v>
@@ -3225,7 +3225,7 @@
         <v>0.46875</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9185303003362743</v>
+        <v>0.9185303003362744</v>
       </c>
       <c r="E162" t="n">
         <v>0.7395352005136978</v>
@@ -3244,7 +3244,7 @@
         <v>0.46875</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9405333228759577</v>
+        <v>0.9405333228759576</v>
       </c>
       <c r="E163" t="n">
         <v>0.7589177341313434</v>
@@ -3263,7 +3263,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="D164" t="n">
-        <v>0.9823322045432281</v>
+        <v>0.982332204543228</v>
       </c>
       <c r="E164" t="n">
         <v>0.7792512970967387</v>
@@ -3282,7 +3282,7 @@
         <v>0.4375000000000001</v>
       </c>
       <c r="D165" t="n">
-        <v>0.9844349745515915</v>
+        <v>0.9844349745515916</v>
       </c>
       <c r="E165" t="n">
         <v>0.7591188870995266</v>
@@ -3317,7 +3317,7 @@
         <v>0.8915662650602411</v>
       </c>
       <c r="C167" t="n">
-        <v>0.3750000000000001</v>
+        <v>0.375</v>
       </c>
       <c r="D167" t="n">
         <v>0.908477471644922</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.9156626506024097</v>
+        <v>0.9156626506024096</v>
       </c>
       <c r="C168" t="n">
         <v>0.4999999999999999</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.9397590361445783</v>
+        <v>0.9397590361445785</v>
       </c>
       <c r="C171" t="n">
         <v>0.625</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.9638554216867473</v>
+        <v>0.9638554216867472</v>
       </c>
       <c r="C172" t="n">
         <v>0.6875</v>
@@ -3453,7 +3453,7 @@
         <v>0.78125</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9940035084602725</v>
+        <v>0.9940035084602724</v>
       </c>
       <c r="E174" t="n">
         <v>0.9090202457919784</v>
@@ -3529,10 +3529,10 @@
         <v>0.84375</v>
       </c>
       <c r="D178" t="n">
-        <v>0.9929551033202063</v>
+        <v>0.9929551033202064</v>
       </c>
       <c r="E178" t="n">
-        <v>0.9346988025560109</v>
+        <v>0.9346988025560108</v>
       </c>
     </row>
     <row r="179">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.9891304347826085</v>
+        <v>0.9891304347826084</v>
       </c>
       <c r="C179" t="n">
         <v>0.8749999999999999</v>
@@ -3564,13 +3564,13 @@
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>0.9062500000000001</v>
+        <v>0.90625</v>
       </c>
       <c r="D180" t="n">
-        <v>0.9922248499806769</v>
+        <v>0.99175252624052</v>
       </c>
       <c r="E180" t="n">
-        <v>0.9661582833268924</v>
+        <v>0.9660008420801732</v>
       </c>
     </row>
     <row r="181">
@@ -3590,25 +3590,6 @@
       </c>
       <c r="E181" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>0.9684210526315788</v>
-      </c>
-      <c r="C182" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0.954831548220203</v>
-      </c>
-      <c r="E182" t="n">
-        <v>0.9535842002839273</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3660,7 +3641,7 @@
         <v>5.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2144837064952339</v>
+        <v>0.2144837064952338</v>
       </c>
     </row>
     <row r="3">
@@ -3676,7 +3657,7 @@
         <v>5.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.216318931938421</v>
+        <v>0.2163189319384209</v>
       </c>
     </row>
     <row r="4">
@@ -3708,7 +3689,7 @@
         <v>5.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2158826655184728</v>
+        <v>0.2158826655184727</v>
       </c>
     </row>
     <row r="6">
@@ -3772,7 +3753,7 @@
         <v>6.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2179910005812397</v>
+        <v>0.2179910005812396</v>
       </c>
     </row>
     <row r="10">
@@ -3788,7 +3769,7 @@
         <v>6.6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2182622171978539</v>
+        <v>0.2182622171978538</v>
       </c>
     </row>
     <row r="11">
@@ -3804,7 +3785,7 @@
         <v>6.7</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2133141087974606</v>
+        <v>0.2133141087974605</v>
       </c>
     </row>
     <row r="12">
@@ -3868,7 +3849,7 @@
         <v>7.1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2221233325942454</v>
+        <v>0.2221233325942453</v>
       </c>
     </row>
     <row r="16">
@@ -3884,7 +3865,7 @@
         <v>7.2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.220769753883536</v>
+        <v>0.2207697538835359</v>
       </c>
     </row>
     <row r="17">
@@ -3900,7 +3881,7 @@
         <v>7.1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2197200510871163</v>
+        <v>0.2197200510871162</v>
       </c>
     </row>
     <row r="18">
@@ -3916,7 +3897,7 @@
         <v>7.2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2177195914744852</v>
+        <v>0.2177195914744851</v>
       </c>
     </row>
     <row r="19">
@@ -4044,7 +4025,7 @@
         <v>6.6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2181028585196967</v>
+        <v>0.2181028585196966</v>
       </c>
     </row>
     <row r="27">
@@ -4076,7 +4057,7 @@
         <v>6.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2172222433013914</v>
+        <v>0.2172222433013913</v>
       </c>
     </row>
     <row r="29">
@@ -4092,7 +4073,7 @@
         <v>6.3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2178010163122744</v>
+        <v>0.2178010163122743</v>
       </c>
     </row>
     <row r="30">
@@ -4124,7 +4105,7 @@
         <v>6.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2167167319171494</v>
+        <v>0.2167167319171493</v>
       </c>
     </row>
     <row r="32">
@@ -4172,7 +4153,7 @@
         <v>5.7</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2187602876319878</v>
+        <v>0.2187602876319877</v>
       </c>
     </row>
     <row r="35">
@@ -4220,7 +4201,7 @@
         <v>5.6</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2202994011171443</v>
+        <v>0.2202994011171442</v>
       </c>
     </row>
     <row r="38">
@@ -4236,7 +4217,7 @@
         <v>5.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2224782495762383</v>
+        <v>0.2224782495762382</v>
       </c>
     </row>
     <row r="39">
@@ -4252,7 +4233,7 @@
         <v>5.6</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2254332403816362</v>
+        <v>0.2254332403816361</v>
       </c>
     </row>
     <row r="40">
@@ -4268,7 +4249,7 @@
         <v>5.7</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2249205544331556</v>
+        <v>0.2249205544331555</v>
       </c>
     </row>
     <row r="41">
@@ -4284,7 +4265,7 @@
         <v>5.6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2274453362709764</v>
+        <v>0.2274453362709763</v>
       </c>
     </row>
     <row r="42">
@@ -4300,7 +4281,7 @@
         <v>5.7</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2247464567387061</v>
+        <v>0.224746456738706</v>
       </c>
     </row>
     <row r="43">
@@ -4316,7 +4297,7 @@
         <v>5.7</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2248368217595582</v>
+        <v>0.2248368217595581</v>
       </c>
     </row>
     <row r="44">
@@ -4332,7 +4313,7 @@
         <v>5.7</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2254800353761997</v>
+        <v>0.2254800353761996</v>
       </c>
     </row>
     <row r="45">
@@ -4396,7 +4377,7 @@
         <v>5.3</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2186584209756129</v>
+        <v>0.2186584209756128</v>
       </c>
     </row>
     <row r="49">
@@ -4460,7 +4441,7 @@
         <v>5.4</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2264056574507284</v>
+        <v>0.2264056574507283</v>
       </c>
     </row>
     <row r="53">
@@ -4556,7 +4537,7 @@
         <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2285970857885173</v>
+        <v>0.2285970857885172</v>
       </c>
     </row>
     <row r="59">
@@ -4732,7 +4713,7 @@
         <v>6.2</v>
       </c>
       <c r="D69" t="n">
-        <v>0.227739378996592</v>
+        <v>0.2277393789965919</v>
       </c>
     </row>
     <row r="70">
@@ -4812,7 +4793,7 @@
         <v>5.9</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2186286523599865</v>
+        <v>0.2186286523599864</v>
       </c>
     </row>
     <row r="75">
@@ -4844,7 +4825,7 @@
         <v>5.9</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2191753307115642</v>
+        <v>0.2191753307115641</v>
       </c>
     </row>
     <row r="77">
@@ -4860,7 +4841,7 @@
         <v>5.7</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2175911308009368</v>
+        <v>0.2175911308009367</v>
       </c>
     </row>
     <row r="78">
@@ -4876,7 +4857,7 @@
         <v>5.7</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2161574089217935</v>
+        <v>0.2161574089217934</v>
       </c>
     </row>
     <row r="79">
@@ -4892,7 +4873,7 @@
         <v>5.7</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2146095360080125</v>
+        <v>0.2146095360080124</v>
       </c>
     </row>
     <row r="80">
@@ -4908,7 +4889,7 @@
         <v>5.6</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2135497203635996</v>
+        <v>0.2135497203635995</v>
       </c>
     </row>
     <row r="81">
@@ -4956,7 +4937,7 @@
         <v>5.2</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2027358661530098</v>
+        <v>0.2027358661530097</v>
       </c>
     </row>
     <row r="84">
@@ -4972,7 +4953,7 @@
         <v>5.2</v>
       </c>
       <c r="D84" t="n">
-        <v>0.2048076210931714</v>
+        <v>0.2048076210931713</v>
       </c>
     </row>
     <row r="85">
@@ -5020,7 +5001,7 @@
         <v>5.1</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2087065635519888</v>
+        <v>0.2087065635519887</v>
       </c>
     </row>
     <row r="88">
@@ -5036,7 +5017,7 @@
         <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2070763939707692</v>
+        <v>0.2070763939707691</v>
       </c>
     </row>
     <row r="89">
@@ -5100,7 +5081,7 @@
         <v>4.9</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2032500016506408</v>
+        <v>0.2032500016506407</v>
       </c>
     </row>
     <row r="93">
@@ -5116,7 +5097,7 @@
         <v>4.9</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2041420759579269</v>
+        <v>0.2041420759579268</v>
       </c>
     </row>
     <row r="94">
@@ -5132,7 +5113,7 @@
         <v>4.8</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2029127923881969</v>
+        <v>0.2029127923881968</v>
       </c>
     </row>
     <row r="95">
@@ -5196,7 +5177,7 @@
         <v>4.7</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2058670578992161</v>
+        <v>0.205867057899216</v>
       </c>
     </row>
     <row r="99">
@@ -5260,7 +5241,7 @@
         <v>4.8</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2076659636631001</v>
+        <v>0.2076659636631</v>
       </c>
     </row>
     <row r="103">
@@ -5340,7 +5321,7 @@
         <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>0.19896653835297</v>
+        <v>0.1989665383529699</v>
       </c>
     </row>
     <row r="108">
@@ -5420,7 +5401,7 @@
         <v>5.6</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2086829309096993</v>
+        <v>0.2086829309096992</v>
       </c>
     </row>
     <row r="113">
@@ -5452,7 +5433,7 @@
         <v>5.1</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1987019944069678</v>
+        <v>0.1987019944069677</v>
       </c>
     </row>
     <row r="115">
@@ -5468,7 +5449,7 @@
         <v>4.9</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1940492012785181</v>
+        <v>0.194049201278518</v>
       </c>
     </row>
     <row r="116">
@@ -5612,7 +5593,7 @@
         <v>4.1</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1944966162606</v>
+        <v>0.1944966162605999</v>
       </c>
     </row>
     <row r="125">
@@ -5644,7 +5625,7 @@
         <v>4.1</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1961475664806731</v>
+        <v>0.196147566480673</v>
       </c>
     </row>
     <row r="127">
@@ -5724,7 +5705,7 @@
         <v>4.4</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2073371391083059</v>
+        <v>0.2073371391083058</v>
       </c>
     </row>
     <row r="132">
@@ -5788,7 +5769,7 @@
         <v>5</v>
       </c>
       <c r="D135" t="n">
-        <v>0.2230346650151756</v>
+        <v>0.2230346650151755</v>
       </c>
     </row>
     <row r="136">
@@ -5852,7 +5833,7 @@
         <v>5.6</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2255393188876454</v>
+        <v>0.2255393188876453</v>
       </c>
     </row>
     <row r="140">
@@ -5916,7 +5897,7 @@
         <v>5.9</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2257120628881144</v>
+        <v>0.2257120628881143</v>
       </c>
     </row>
     <row r="144">
@@ -5932,7 +5913,7 @@
         <v>6.1</v>
       </c>
       <c r="D144" t="n">
-        <v>0.2282672486775731</v>
+        <v>0.228267248677573</v>
       </c>
     </row>
     <row r="145">
@@ -5964,7 +5945,7 @@
         <v>6.1</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2298259181428325</v>
+        <v>0.2298259181428324</v>
       </c>
     </row>
     <row r="147">
@@ -5980,7 +5961,7 @@
         <v>6.2</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2328904567233725</v>
+        <v>0.2328904567233724</v>
       </c>
     </row>
     <row r="148">
@@ -6076,7 +6057,7 @@
         <v>5.9</v>
       </c>
       <c r="D153" t="n">
-        <v>0.2265726951791928</v>
+        <v>0.2265726951791927</v>
       </c>
     </row>
     <row r="154">
@@ -6108,7 +6089,7 @@
         <v>5.6</v>
       </c>
       <c r="D155" t="n">
-        <v>0.2207881384697674</v>
+        <v>0.2207881384697673</v>
       </c>
     </row>
     <row r="156">
@@ -6124,7 +6105,7 @@
         <v>5.5</v>
       </c>
       <c r="D156" t="n">
-        <v>0.2253823067762058</v>
+        <v>0.2253823067762057</v>
       </c>
     </row>
     <row r="157">
@@ -6140,7 +6121,7 @@
         <v>5.5</v>
       </c>
       <c r="D157" t="n">
-        <v>0.2291800617182597</v>
+        <v>0.2291800617182596</v>
       </c>
     </row>
     <row r="158">
@@ -6156,7 +6137,7 @@
         <v>5.4</v>
       </c>
       <c r="D158" t="n">
-        <v>0.2309754226259297</v>
+        <v>0.2309754226259296</v>
       </c>
     </row>
     <row r="159">
@@ -6172,7 +6153,7 @@
         <v>5.5</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2314148940180176</v>
+        <v>0.2314148940180175</v>
       </c>
     </row>
     <row r="160">
@@ -6380,7 +6361,7 @@
         <v>6.2</v>
       </c>
       <c r="D172" t="n">
-        <v>0.2426468029894171</v>
+        <v>0.242646802989417</v>
       </c>
     </row>
     <row r="173">
@@ -6412,7 +6393,7 @@
         <v>6.5</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2433142716617252</v>
+        <v>0.2433142716617251</v>
       </c>
     </row>
     <row r="175">
@@ -6428,7 +6409,7 @@
         <v>6.8</v>
       </c>
       <c r="D175" t="n">
-        <v>0.2445324170963497</v>
+        <v>0.2445324170963496</v>
       </c>
     </row>
     <row r="176">
@@ -6444,7 +6425,7 @@
         <v>6.7</v>
       </c>
       <c r="D176" t="n">
-        <v>0.2458421710504727</v>
+        <v>0.2458421710504726</v>
       </c>
     </row>
     <row r="177">
@@ -6508,7 +6489,7 @@
         <v>6.9</v>
       </c>
       <c r="D180" t="n">
-        <v>0.2474092835719974</v>
+        <v>0.2473780901728729</v>
       </c>
     </row>
     <row r="181">
@@ -6518,29 +6499,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="C181" t="n">
         <v>7.2</v>
       </c>
       <c r="D181" t="n">
-        <v>0.2514723625654082</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="C182" t="n">
-        <v>7</v>
-      </c>
-      <c r="D182" t="n">
-        <v>0.2483289996014</v>
+        <v>0.2513878650925042</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/idc_data.xlsx
+++ b/data/processed/idc_data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -847,13 +847,13 @@
         <v>0.2272727272727273</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0588235294117644</v>
+        <v>0.05882352941176449</v>
       </c>
       <c r="D37" t="n">
         <v>0.8309695443551434</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3723552670132117</v>
+        <v>0.3723552670132118</v>
       </c>
     </row>
     <row r="38">
@@ -866,7 +866,7 @@
         <v>0.1818181818181812</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0588235294117644</v>
+        <v>0.05882352941176449</v>
       </c>
       <c r="D38" t="n">
         <v>1</v>
@@ -885,7 +885,7 @@
         <v>0.1818181818181812</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0588235294117644</v>
+        <v>0.05882352941176449</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
@@ -923,7 +923,7 @@
         <v>0.2727272727272735</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0588235294117644</v>
+        <v>0.05882352941176449</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3181818181818179</v>
+        <v>0.318181818181818</v>
       </c>
       <c r="C42" t="n">
         <v>0.1176470588235295</v>
@@ -948,7 +948,7 @@
         <v>0.8324983307105308</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4227757359052927</v>
+        <v>0.4227757359052928</v>
       </c>
     </row>
     <row r="43">
@@ -999,7 +999,7 @@
         <v>0.2727272727272735</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0588235294117644</v>
+        <v>0.05882352941176449</v>
       </c>
       <c r="D45" t="n">
         <v>0.7830522467498834</v>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4090909090909085</v>
+        <v>0.4090909090909086</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
@@ -1059,10 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4546540657780137</v>
+        <v>0.4546540657780138</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4242786279866108</v>
+        <v>0.4242786279866109</v>
       </c>
     </row>
     <row r="49">
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9545454545454556</v>
+        <v>0.9545454545454555</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0499999999999998</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9191340608899672</v>
+        <v>0.9191340608899673</v>
       </c>
       <c r="E51" t="n">
         <v>0.6412265051451409</v>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9545454545454556</v>
+        <v>0.9545454545454555</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="D52" t="n">
         <v>0.9354739862101402</v>
@@ -1148,13 +1148,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9545454545454556</v>
+        <v>0.9545454545454555</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0499999999999998</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9759592328097708</v>
+        <v>0.9759592328097707</v>
       </c>
       <c r="E53" t="n">
         <v>0.6601682291184087</v>
@@ -1170,7 +1170,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="D54" t="n">
         <v>0.8883007681125101</v>
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4400000000000005</v>
+        <v>0.4400000000000006</v>
       </c>
       <c r="C60" t="n">
         <v>0.5</v>
@@ -1325,7 +1325,7 @@
         <v>0.5</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9725506805246664</v>
+        <v>0.9725506805246665</v>
       </c>
       <c r="E62" t="n">
         <v>0.6908502268415555</v>
@@ -1363,7 +1363,7 @@
         <v>0.5499999999999998</v>
       </c>
       <c r="D64" t="n">
-        <v>0.97499432097947</v>
+        <v>0.9749943209794701</v>
       </c>
       <c r="E64" t="n">
         <v>0.7349981069931566</v>
@@ -1382,7 +1382,7 @@
         <v>0.5</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9310890047696612</v>
+        <v>0.9310890047696613</v>
       </c>
       <c r="E65" t="n">
         <v>0.7170296682565538</v>
@@ -1499,7 +1499,7 @@
         <v>0.1978798745881518</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3326266248627172</v>
+        <v>0.3326266248627173</v>
       </c>
     </row>
     <row r="72">
@@ -1556,7 +1556,7 @@
         <v>0.3628231483643701</v>
       </c>
       <c r="E74" t="n">
-        <v>0.3309410494547899</v>
+        <v>0.33094104945479</v>
       </c>
     </row>
     <row r="75">
@@ -1566,13 +1566,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.1200000000000002</v>
+        <v>0.1200000000000003</v>
       </c>
       <c r="C75" t="n">
         <v>0.2999999999999998</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4356421767454645</v>
+        <v>0.4356421767454646</v>
       </c>
       <c r="E75" t="n">
         <v>0.2852140589151549</v>
@@ -1629,10 +1629,10 @@
         <v>0.25</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2399283557599175</v>
+        <v>0.2399283557599176</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2003464889570096</v>
+        <v>0.2003464889570097</v>
       </c>
     </row>
     <row r="79">
@@ -1648,7 +1648,7 @@
         <v>0.25</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1629527256875272</v>
+        <v>0.1629527256875273</v>
       </c>
       <c r="E79" t="n">
         <v>0.2117249826365829</v>
@@ -1670,7 +1670,7 @@
         <v>0.1102481552651509</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2021814838538157</v>
+        <v>0.2021814838538158</v>
       </c>
     </row>
     <row r="81">
@@ -1702,7 +1702,7 @@
         <v>0.1111111111111114</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.0370370370370362</v>
+        <v>0.03703703703703626</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.0123456790123454</v>
+        <v>0.01234567901234542</v>
       </c>
     </row>
     <row r="84">
@@ -1743,10 +1743,10 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.07217268456268749</v>
+        <v>0.07217268456268752</v>
       </c>
       <c r="E84" t="n">
-        <v>0.0240575615208958</v>
+        <v>0.02405756152089584</v>
       </c>
     </row>
     <row r="85">
@@ -1765,7 +1765,7 @@
         <v>0.2373397296057668</v>
       </c>
       <c r="E85" t="n">
-        <v>0.0791132432019222</v>
+        <v>0.07911324320192227</v>
       </c>
     </row>
     <row r="86">
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.0357142857142862</v>
+        <v>0.03571428571428621</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1736702105847081</v>
+        <v>0.1736702105847082</v>
       </c>
       <c r="E86" t="n">
-        <v>0.06979483209966469</v>
+        <v>0.06979483209966479</v>
       </c>
     </row>
     <row r="87">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.1428571428571435</v>
+        <v>0.1428571428571436</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1512087838932728</v>
+        <v>0.1512087838932729</v>
       </c>
       <c r="E88" t="n">
         <v>0.1337362612977575</v>
@@ -1838,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.1751051323246209</v>
+        <v>0.175105132324621</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1655112345843976</v>
+        <v>0.1655112345843977</v>
       </c>
     </row>
     <row r="90">
@@ -1854,13 +1854,13 @@
         <v>0.2142857142857147</v>
       </c>
       <c r="C90" t="n">
-        <v>0.043478260869565</v>
+        <v>0.04347826086956506</v>
       </c>
       <c r="D90" t="n">
-        <v>0.09045990357805481</v>
+        <v>0.09045990357805485</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1160746262444448</v>
+        <v>0.1160746262444449</v>
       </c>
     </row>
     <row r="91">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1071428571428573</v>
+        <v>0.1071428571428574</v>
       </c>
       <c r="C91" t="n">
-        <v>0.043478260869565</v>
+        <v>0.04347826086956506</v>
       </c>
       <c r="D91" t="n">
-        <v>0.0383129816107087</v>
+        <v>0.03831298161070876</v>
       </c>
       <c r="E91" t="n">
-        <v>0.06297803320771039</v>
+        <v>0.06297803320771041</v>
       </c>
     </row>
     <row r="92">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.1428571428571435</v>
+        <v>0.1428571428571436</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0179106796724274</v>
+        <v>0.01791067967242742</v>
       </c>
       <c r="E92" t="n">
-        <v>0.0535892741765236</v>
+        <v>0.05358927417652367</v>
       </c>
     </row>
     <row r="93">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.1071428571428573</v>
+        <v>0.1071428571428574</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0489874235180162</v>
+        <v>0.04898742351801629</v>
       </c>
       <c r="E93" t="n">
-        <v>0.0520434268869578</v>
+        <v>0.05204342688695789</v>
       </c>
     </row>
     <row r="94">
@@ -1933,10 +1933,10 @@
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0.0061634902446653</v>
+        <v>0.006163490244665353</v>
       </c>
       <c r="E94" t="n">
-        <v>0.0615783062720312</v>
+        <v>0.06157830627203129</v>
       </c>
     </row>
     <row r="95">
@@ -1971,10 +1971,10 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.123980471048117</v>
+        <v>0.1239804710481171</v>
       </c>
       <c r="E96" t="n">
-        <v>0.148469680825563</v>
+        <v>0.1484696808255631</v>
       </c>
     </row>
     <row r="97">
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2448778821631854</v>
+        <v>0.2448778821631855</v>
       </c>
       <c r="E97" t="n">
         <v>0.2125783416734429</v>
@@ -2012,7 +2012,7 @@
         <v>0.2320166827458945</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2082912752010125</v>
+        <v>0.2082912752010126</v>
       </c>
     </row>
     <row r="99">
@@ -2028,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2854673416493078</v>
+        <v>0.2854673416493079</v>
       </c>
       <c r="E99" t="n">
         <v>0.2856319710259599</v>
@@ -2044,13 +2044,13 @@
         <v>0.6785714285714292</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0399999999999998</v>
+        <v>0.03999999999999986</v>
       </c>
       <c r="D100" t="n">
         <v>0.2905293572727042</v>
       </c>
       <c r="E100" t="n">
-        <v>0.336366928614711</v>
+        <v>0.3363669286147111</v>
       </c>
     </row>
     <row r="101">
@@ -2063,7 +2063,7 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0399999999999998</v>
+        <v>0.03999999999999986</v>
       </c>
       <c r="D101" t="n">
         <v>0.3513175817075109</v>
@@ -2082,7 +2082,7 @@
         <v>0.8999999999999998</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0399999999999998</v>
+        <v>0.03999999999999986</v>
       </c>
       <c r="D102" t="n">
         <v>0.2860368403049701</v>
@@ -2101,7 +2101,7 @@
         <v>0.9333333333333336</v>
       </c>
       <c r="C103" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="D103" t="n">
         <v>0.2805459391879865</v>
@@ -2123,7 +2123,7 @@
         <v>0.1199999999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2809435606936264</v>
+        <v>0.2809435606936265</v>
       </c>
       <c r="E104" t="n">
         <v>0.3558700757867643</v>
@@ -2164,7 +2164,7 @@
         <v>0.1981927225528276</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2393975741842757</v>
+        <v>0.2393975741842758</v>
       </c>
     </row>
     <row r="107">
@@ -2180,10 +2180,10 @@
         <v>0.1199999999999999</v>
       </c>
       <c r="D107" t="n">
-        <v>0.0247978497132711</v>
+        <v>0.02479784971327119</v>
       </c>
       <c r="E107" t="n">
-        <v>0.1371548387933126</v>
+        <v>0.1371548387933127</v>
       </c>
     </row>
     <row r="108">
@@ -2196,7 +2196,7 @@
         <v>0.2666666666666669</v>
       </c>
       <c r="C108" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="D108" t="n">
         <v>0.1035980211576326</v>
@@ -2215,10 +2215,10 @@
         <v>0.2333333333333331</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1599999999999997</v>
+        <v>0.1599999999999998</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2048299465559414</v>
+        <v>0.2048299465559415</v>
       </c>
       <c r="E109" t="n">
         <v>0.1993877599630914</v>
@@ -2253,13 +2253,13 @@
         <v>0.3999999999999997</v>
       </c>
       <c r="C111" t="n">
-        <v>0.3199999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="D111" t="n">
         <v>0.4283229775251577</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3827743258417191</v>
+        <v>0.3827743258417192</v>
       </c>
     </row>
     <row r="112">
@@ -2272,10 +2272,10 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3599999999999997</v>
+        <v>0.3599999999999998</v>
       </c>
       <c r="D112" t="n">
-        <v>0.316575811270907</v>
+        <v>0.3165758112709071</v>
       </c>
       <c r="E112" t="n">
         <v>0.2255252704236356</v>
@@ -2291,13 +2291,13 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2399999999999998</v>
+        <v>0.2399999999999999</v>
       </c>
       <c r="D113" t="n">
         <v>0.1678060787477241</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1359353595825746</v>
+        <v>0.1359353595825747</v>
       </c>
     </row>
     <row r="114">
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1599999999999997</v>
+        <v>0.1599999999999998</v>
       </c>
       <c r="D114" t="n">
-        <v>0.0168537395040272</v>
+        <v>0.01685373950402727</v>
       </c>
       <c r="E114" t="n">
-        <v>0.0589512465013423</v>
+        <v>0.05895124650134235</v>
       </c>
     </row>
     <row r="115">
@@ -2329,13 +2329,13 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000007</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0.0266666666666666</v>
+        <v>0.02666666666666669</v>
       </c>
     </row>
     <row r="116">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.0588235294117641</v>
+        <v>0.05882352941176417</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>0.0196078431372547</v>
+        <v>0.01960784313725472</v>
       </c>
     </row>
     <row r="117">
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0.0588235294117646</v>
+        <v>0.05882352941176464</v>
       </c>
     </row>
     <row r="118">
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1568627450980391</v>
+        <v>0.1568627450980392</v>
       </c>
     </row>
     <row r="120">
@@ -2468,7 +2468,7 @@
         <v>0.2153533575103212</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2482550407387345</v>
+        <v>0.2482550407387346</v>
       </c>
     </row>
     <row r="123">
@@ -2500,7 +2500,7 @@
         <v>0.6078431372549018</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0312499999999998</v>
+        <v>0.03124999999999989</v>
       </c>
       <c r="D124" t="n">
         <v>0.2545599775084994</v>
@@ -2525,7 +2525,7 @@
         <v>0.2814720600383868</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3029743468101812</v>
+        <v>0.3029743468101813</v>
       </c>
     </row>
     <row r="126">
@@ -2538,7 +2538,7 @@
         <v>0.7058823529411763</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0312499999999998</v>
+        <v>0.03124999999999989</v>
       </c>
       <c r="D126" t="n">
         <v>0.2878714351788128</v>
@@ -2557,7 +2557,7 @@
         <v>0.7843137254901964</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0312499999999998</v>
+        <v>0.03124999999999989</v>
       </c>
       <c r="D127" t="n">
         <v>0.3567797887508668</v>
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.9607843137254904</v>
+        <v>0.9607843137254903</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0625</v>
+        <v>0.06250000000000006</v>
       </c>
       <c r="D128" t="n">
         <v>0.4338893293994195</v>
       </c>
       <c r="E128" t="n">
-        <v>0.4857245477083032</v>
+        <v>0.4857245477083033</v>
       </c>
     </row>
     <row r="129">
@@ -2595,7 +2595,7 @@
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0625</v>
+        <v>0.06250000000000006</v>
       </c>
       <c r="D129" t="n">
         <v>0.5109885971651589</v>
@@ -2614,7 +2614,7 @@
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0937499999999999</v>
+        <v>0.09374999999999994</v>
       </c>
       <c r="D130" t="n">
         <v>0.5224447035496396</v>
@@ -2671,7 +2671,7 @@
         <v>0.9242424242424242</v>
       </c>
       <c r="C133" t="n">
-        <v>0.21875</v>
+        <v>0.2187500000000001</v>
       </c>
       <c r="D133" t="n">
         <v>0.7999634422509253</v>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.9545454545454544</v>
+        <v>0.9545454545454545</v>
       </c>
       <c r="C137" t="n">
-        <v>0.375</v>
+        <v>0.3750000000000001</v>
       </c>
       <c r="D137" t="n">
         <v>0.8621984129111688</v>
@@ -2826,7 +2826,7 @@
         <v>0.5624999999999999</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9434585701441284</v>
+        <v>0.9434585701441283</v>
       </c>
       <c r="E141" t="n">
         <v>0.8353195233813761</v>
@@ -2845,7 +2845,7 @@
         <v>0.5624999999999999</v>
       </c>
       <c r="D142" t="n">
-        <v>0.93410039035488</v>
+        <v>0.9341003903548799</v>
       </c>
       <c r="E142" t="n">
         <v>0.8322001301182933</v>
@@ -2883,7 +2883,7 @@
         <v>0.6562499999999999</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9359548364085428</v>
+        <v>0.9359548364085427</v>
       </c>
       <c r="E144" t="n">
         <v>0.8640682788028475</v>
@@ -2921,7 +2921,7 @@
         <v>0.6562499999999999</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9534504164253912</v>
+        <v>0.9534504164253911</v>
       </c>
       <c r="E146" t="n">
         <v>0.8699001388084637</v>
@@ -2962,7 +2962,7 @@
         <v>0.987505664722233</v>
       </c>
       <c r="E148" t="n">
-        <v>0.9020852215740776</v>
+        <v>0.9020852215740777</v>
       </c>
     </row>
     <row r="149">
@@ -3016,7 +3016,7 @@
         <v>0.6562499999999999</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9045886593715888</v>
+        <v>0.9045886593715887</v>
       </c>
       <c r="E151" t="n">
         <v>0.8094361796298871</v>
@@ -3168,7 +3168,7 @@
         <v>0.46875</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9710731241272008</v>
+        <v>0.9710731241272009</v>
       </c>
       <c r="E159" t="n">
         <v>0.7369691538255329</v>
@@ -3187,7 +3187,7 @@
         <v>0.46875</v>
       </c>
       <c r="D160" t="n">
-        <v>0.9526198528080616</v>
+        <v>0.9526198528080617</v>
       </c>
       <c r="E160" t="n">
         <v>0.7308180633858198</v>
@@ -3206,7 +3206,7 @@
         <v>0.4375000000000001</v>
       </c>
       <c r="D161" t="n">
-        <v>0.9347747781531665</v>
+        <v>0.9347747781531663</v>
       </c>
       <c r="E161" t="n">
         <v>0.7265012312719391</v>
@@ -3225,7 +3225,7 @@
         <v>0.46875</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9185303003362744</v>
+        <v>0.9185303003362743</v>
       </c>
       <c r="E162" t="n">
         <v>0.7395352005136978</v>
@@ -3244,7 +3244,7 @@
         <v>0.46875</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9405333228759576</v>
+        <v>0.9405333228759577</v>
       </c>
       <c r="E163" t="n">
         <v>0.7589177341313434</v>
@@ -3263,7 +3263,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="D164" t="n">
-        <v>0.982332204543228</v>
+        <v>0.9823322045432281</v>
       </c>
       <c r="E164" t="n">
         <v>0.7792512970967387</v>
@@ -3282,7 +3282,7 @@
         <v>0.4375000000000001</v>
       </c>
       <c r="D165" t="n">
-        <v>0.9844349745515916</v>
+        <v>0.9844349745515915</v>
       </c>
       <c r="E165" t="n">
         <v>0.7591188870995266</v>
@@ -3317,7 +3317,7 @@
         <v>0.8915662650602411</v>
       </c>
       <c r="C167" t="n">
-        <v>0.375</v>
+        <v>0.3750000000000001</v>
       </c>
       <c r="D167" t="n">
         <v>0.908477471644922</v>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.9156626506024096</v>
+        <v>0.9156626506024097</v>
       </c>
       <c r="C168" t="n">
         <v>0.4999999999999999</v>
@@ -3390,7 +3390,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.9397590361445785</v>
+        <v>0.9397590361445783</v>
       </c>
       <c r="C171" t="n">
         <v>0.625</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.9638554216867472</v>
+        <v>0.9638554216867473</v>
       </c>
       <c r="C172" t="n">
         <v>0.6875</v>
@@ -3453,7 +3453,7 @@
         <v>0.78125</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9940035084602724</v>
+        <v>0.9940035084602725</v>
       </c>
       <c r="E174" t="n">
         <v>0.9090202457919784</v>
@@ -3529,10 +3529,10 @@
         <v>0.84375</v>
       </c>
       <c r="D178" t="n">
-        <v>0.9929551033202064</v>
+        <v>0.9929551033202063</v>
       </c>
       <c r="E178" t="n">
-        <v>0.9346988025560108</v>
+        <v>0.9346988025560109</v>
       </c>
     </row>
     <row r="179">
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.9891304347826084</v>
+        <v>0.9891304347826085</v>
       </c>
       <c r="C179" t="n">
         <v>0.8749999999999999</v>
@@ -3564,13 +3564,13 @@
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>0.90625</v>
+        <v>0.9062500000000001</v>
       </c>
       <c r="D180" t="n">
-        <v>0.99175252624052</v>
+        <v>0.9922248499806769</v>
       </c>
       <c r="E180" t="n">
-        <v>0.9660008420801732</v>
+        <v>0.9661582833268924</v>
       </c>
     </row>
     <row r="181">
@@ -3590,6 +3590,25 @@
       </c>
       <c r="E181" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0.9684210526315788</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.954831548220203</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.9535842002839273</v>
       </c>
     </row>
   </sheetData>
@@ -3603,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3641,7 +3660,7 @@
         <v>5.5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2144837064952338</v>
+        <v>0.2144837064952339</v>
       </c>
     </row>
     <row r="3">
@@ -3657,7 +3676,7 @@
         <v>5.7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2163189319384209</v>
+        <v>0.216318931938421</v>
       </c>
     </row>
     <row r="4">
@@ -3689,7 +3708,7 @@
         <v>5.9</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2158826655184727</v>
+        <v>0.2158826655184728</v>
       </c>
     </row>
     <row r="6">
@@ -3753,7 +3772,7 @@
         <v>6.5</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2179910005812396</v>
+        <v>0.2179910005812397</v>
       </c>
     </row>
     <row r="10">
@@ -3769,7 +3788,7 @@
         <v>6.6</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2182622171978538</v>
+        <v>0.2182622171978539</v>
       </c>
     </row>
     <row r="11">
@@ -3785,7 +3804,7 @@
         <v>6.7</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2133141087974605</v>
+        <v>0.2133141087974606</v>
       </c>
     </row>
     <row r="12">
@@ -3849,7 +3868,7 @@
         <v>7.1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2221233325942453</v>
+        <v>0.2221233325942454</v>
       </c>
     </row>
     <row r="16">
@@ -3865,7 +3884,7 @@
         <v>7.2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2207697538835359</v>
+        <v>0.220769753883536</v>
       </c>
     </row>
     <row r="17">
@@ -3881,7 +3900,7 @@
         <v>7.1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2197200510871162</v>
+        <v>0.2197200510871163</v>
       </c>
     </row>
     <row r="18">
@@ -3897,7 +3916,7 @@
         <v>7.2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2177195914744851</v>
+        <v>0.2177195914744852</v>
       </c>
     </row>
     <row r="19">
@@ -4025,7 +4044,7 @@
         <v>6.6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2181028585196966</v>
+        <v>0.2181028585196967</v>
       </c>
     </row>
     <row r="27">
@@ -4057,7 +4076,7 @@
         <v>6.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2172222433013913</v>
+        <v>0.2172222433013914</v>
       </c>
     </row>
     <row r="29">
@@ -4073,7 +4092,7 @@
         <v>6.3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2178010163122743</v>
+        <v>0.2178010163122744</v>
       </c>
     </row>
     <row r="30">
@@ -4105,7 +4124,7 @@
         <v>6.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2167167319171493</v>
+        <v>0.2167167319171494</v>
       </c>
     </row>
     <row r="32">
@@ -4153,7 +4172,7 @@
         <v>5.7</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2187602876319877</v>
+        <v>0.2187602876319878</v>
       </c>
     </row>
     <row r="35">
@@ -4201,7 +4220,7 @@
         <v>5.6</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2202994011171442</v>
+        <v>0.2202994011171443</v>
       </c>
     </row>
     <row r="38">
@@ -4217,7 +4236,7 @@
         <v>5.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2224782495762382</v>
+        <v>0.2224782495762383</v>
       </c>
     </row>
     <row r="39">
@@ -4233,7 +4252,7 @@
         <v>5.6</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2254332403816361</v>
+        <v>0.2254332403816362</v>
       </c>
     </row>
     <row r="40">
@@ -4249,7 +4268,7 @@
         <v>5.7</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2249205544331555</v>
+        <v>0.2249205544331556</v>
       </c>
     </row>
     <row r="41">
@@ -4265,7 +4284,7 @@
         <v>5.6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2274453362709763</v>
+        <v>0.2274453362709764</v>
       </c>
     </row>
     <row r="42">
@@ -4281,7 +4300,7 @@
         <v>5.7</v>
       </c>
       <c r="D42" t="n">
-        <v>0.224746456738706</v>
+        <v>0.2247464567387061</v>
       </c>
     </row>
     <row r="43">
@@ -4297,7 +4316,7 @@
         <v>5.7</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2248368217595581</v>
+        <v>0.2248368217595582</v>
       </c>
     </row>
     <row r="44">
@@ -4313,7 +4332,7 @@
         <v>5.7</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2254800353761996</v>
+        <v>0.2254800353761997</v>
       </c>
     </row>
     <row r="45">
@@ -4377,7 +4396,7 @@
         <v>5.3</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2186584209756128</v>
+        <v>0.2186584209756129</v>
       </c>
     </row>
     <row r="49">
@@ -4441,7 +4460,7 @@
         <v>5.4</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2264056574507283</v>
+        <v>0.2264056574507284</v>
       </c>
     </row>
     <row r="53">
@@ -4537,7 +4556,7 @@
         <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2285970857885172</v>
+        <v>0.2285970857885173</v>
       </c>
     </row>
     <row r="59">
@@ -4713,7 +4732,7 @@
         <v>6.2</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2277393789965919</v>
+        <v>0.227739378996592</v>
       </c>
     </row>
     <row r="70">
@@ -4793,7 +4812,7 @@
         <v>5.9</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2186286523599864</v>
+        <v>0.2186286523599865</v>
       </c>
     </row>
     <row r="75">
@@ -4825,7 +4844,7 @@
         <v>5.9</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2191753307115641</v>
+        <v>0.2191753307115642</v>
       </c>
     </row>
     <row r="77">
@@ -4841,7 +4860,7 @@
         <v>5.7</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2175911308009367</v>
+        <v>0.2175911308009368</v>
       </c>
     </row>
     <row r="78">
@@ -4857,7 +4876,7 @@
         <v>5.7</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2161574089217934</v>
+        <v>0.2161574089217935</v>
       </c>
     </row>
     <row r="79">
@@ -4873,7 +4892,7 @@
         <v>5.7</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2146095360080124</v>
+        <v>0.2146095360080125</v>
       </c>
     </row>
     <row r="80">
@@ -4889,7 +4908,7 @@
         <v>5.6</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2135497203635995</v>
+        <v>0.2135497203635996</v>
       </c>
     </row>
     <row r="81">
@@ -4937,7 +4956,7 @@
         <v>5.2</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2027358661530097</v>
+        <v>0.2027358661530098</v>
       </c>
     </row>
     <row r="84">
@@ -4953,7 +4972,7 @@
         <v>5.2</v>
       </c>
       <c r="D84" t="n">
-        <v>0.2048076210931713</v>
+        <v>0.2048076210931714</v>
       </c>
     </row>
     <row r="85">
@@ -5001,7 +5020,7 @@
         <v>5.1</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2087065635519887</v>
+        <v>0.2087065635519888</v>
       </c>
     </row>
     <row r="88">
@@ -5017,7 +5036,7 @@
         <v>5</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2070763939707691</v>
+        <v>0.2070763939707692</v>
       </c>
     </row>
     <row r="89">
@@ -5081,7 +5100,7 @@
         <v>4.9</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2032500016506407</v>
+        <v>0.2032500016506408</v>
       </c>
     </row>
     <row r="93">
@@ -5097,7 +5116,7 @@
         <v>4.9</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2041420759579268</v>
+        <v>0.2041420759579269</v>
       </c>
     </row>
     <row r="94">
@@ -5113,7 +5132,7 @@
         <v>4.8</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2029127923881968</v>
+        <v>0.2029127923881969</v>
       </c>
     </row>
     <row r="95">
@@ -5177,7 +5196,7 @@
         <v>4.7</v>
       </c>
       <c r="D98" t="n">
-        <v>0.205867057899216</v>
+        <v>0.2058670578992161</v>
       </c>
     </row>
     <row r="99">
@@ -5241,7 +5260,7 @@
         <v>4.8</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2076659636631</v>
+        <v>0.2076659636631001</v>
       </c>
     </row>
     <row r="103">
@@ -5321,7 +5340,7 @@
         <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>0.1989665383529699</v>
+        <v>0.19896653835297</v>
       </c>
     </row>
     <row r="108">
@@ -5401,7 +5420,7 @@
         <v>5.6</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2086829309096992</v>
+        <v>0.2086829309096993</v>
       </c>
     </row>
     <row r="113">
@@ -5433,7 +5452,7 @@
         <v>5.1</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1987019944069677</v>
+        <v>0.1987019944069678</v>
       </c>
     </row>
     <row r="115">
@@ -5449,7 +5468,7 @@
         <v>4.9</v>
       </c>
       <c r="D115" t="n">
-        <v>0.194049201278518</v>
+        <v>0.1940492012785181</v>
       </c>
     </row>
     <row r="116">
@@ -5593,7 +5612,7 @@
         <v>4.1</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1944966162605999</v>
+        <v>0.1944966162606</v>
       </c>
     </row>
     <row r="125">
@@ -5625,7 +5644,7 @@
         <v>4.1</v>
       </c>
       <c r="D126" t="n">
-        <v>0.196147566480673</v>
+        <v>0.1961475664806731</v>
       </c>
     </row>
     <row r="127">
@@ -5705,7 +5724,7 @@
         <v>4.4</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2073371391083058</v>
+        <v>0.2073371391083059</v>
       </c>
     </row>
     <row r="132">
@@ -5769,7 +5788,7 @@
         <v>5</v>
       </c>
       <c r="D135" t="n">
-        <v>0.2230346650151755</v>
+        <v>0.2230346650151756</v>
       </c>
     </row>
     <row r="136">
@@ -5833,7 +5852,7 @@
         <v>5.6</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2255393188876453</v>
+        <v>0.2255393188876454</v>
       </c>
     </row>
     <row r="140">
@@ -5897,7 +5916,7 @@
         <v>5.9</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2257120628881143</v>
+        <v>0.2257120628881144</v>
       </c>
     </row>
     <row r="144">
@@ -5913,7 +5932,7 @@
         <v>6.1</v>
       </c>
       <c r="D144" t="n">
-        <v>0.228267248677573</v>
+        <v>0.2282672486775731</v>
       </c>
     </row>
     <row r="145">
@@ -5945,7 +5964,7 @@
         <v>6.1</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2298259181428324</v>
+        <v>0.2298259181428325</v>
       </c>
     </row>
     <row r="147">
@@ -5961,7 +5980,7 @@
         <v>6.2</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2328904567233724</v>
+        <v>0.2328904567233725</v>
       </c>
     </row>
     <row r="148">
@@ -6057,7 +6076,7 @@
         <v>5.9</v>
       </c>
       <c r="D153" t="n">
-        <v>0.2265726951791927</v>
+        <v>0.2265726951791928</v>
       </c>
     </row>
     <row r="154">
@@ -6089,7 +6108,7 @@
         <v>5.6</v>
       </c>
       <c r="D155" t="n">
-        <v>0.2207881384697673</v>
+        <v>0.2207881384697674</v>
       </c>
     </row>
     <row r="156">
@@ -6105,7 +6124,7 @@
         <v>5.5</v>
       </c>
       <c r="D156" t="n">
-        <v>0.2253823067762057</v>
+        <v>0.2253823067762058</v>
       </c>
     </row>
     <row r="157">
@@ -6121,7 +6140,7 @@
         <v>5.5</v>
       </c>
       <c r="D157" t="n">
-        <v>0.2291800617182596</v>
+        <v>0.2291800617182597</v>
       </c>
     </row>
     <row r="158">
@@ -6137,7 +6156,7 @@
         <v>5.4</v>
       </c>
       <c r="D158" t="n">
-        <v>0.2309754226259296</v>
+        <v>0.2309754226259297</v>
       </c>
     </row>
     <row r="159">
@@ -6153,7 +6172,7 @@
         <v>5.5</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2314148940180175</v>
+        <v>0.2314148940180176</v>
       </c>
     </row>
     <row r="160">
@@ -6361,7 +6380,7 @@
         <v>6.2</v>
       </c>
       <c r="D172" t="n">
-        <v>0.242646802989417</v>
+        <v>0.2426468029894171</v>
       </c>
     </row>
     <row r="173">
@@ -6393,7 +6412,7 @@
         <v>6.5</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2433142716617251</v>
+        <v>0.2433142716617252</v>
       </c>
     </row>
     <row r="175">
@@ -6409,7 +6428,7 @@
         <v>6.8</v>
       </c>
       <c r="D175" t="n">
-        <v>0.2445324170963496</v>
+        <v>0.2445324170963497</v>
       </c>
     </row>
     <row r="176">
@@ -6425,7 +6444,7 @@
         <v>6.7</v>
       </c>
       <c r="D176" t="n">
-        <v>0.2458421710504726</v>
+        <v>0.2458421710504727</v>
       </c>
     </row>
     <row r="177">
@@ -6489,7 +6508,7 @@
         <v>6.9</v>
       </c>
       <c r="D180" t="n">
-        <v>0.2473780901728729</v>
+        <v>0.2474092835719974</v>
       </c>
     </row>
     <row r="181">
@@ -6499,13 +6518,29 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="C181" t="n">
         <v>7.2</v>
       </c>
       <c r="D181" t="n">
-        <v>0.2513878650925042</v>
+        <v>0.2514723625654082</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="C182" t="n">
+        <v>7</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.2483289996014</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/idc_data.xlsx
+++ b/data/processed/idc_data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.1818181818181829</v>
       </c>
       <c r="C36" t="n">
         <v>0.1176470588235295</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4015966935060069</v>
+        <v>0.2422116758283082</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2488388265340879</v>
+        <v>0.1805589721566735</v>
       </c>
     </row>
     <row r="37">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.2272727272727273</v>
+        <v>0.1818181818181829</v>
       </c>
       <c r="C37" t="n">
         <v>0.05882352941176449</v>
       </c>
       <c r="D37" t="n">
-        <v>0.8309695443551434</v>
+        <v>0.8452633369830688</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3723552670132118</v>
+        <v>0.3619683494043387</v>
       </c>
     </row>
     <row r="38">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1818181818181812</v>
+        <v>0.1363636363636367</v>
       </c>
       <c r="C38" t="n">
         <v>0.05882352941176449</v>
@@ -872,7 +872,7 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.4135472370766486</v>
+        <v>0.3983957219251337</v>
       </c>
     </row>
     <row r="39">
@@ -882,16 +882,16 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1818181818181812</v>
+        <v>0.1818181818181829</v>
       </c>
       <c r="C39" t="n">
-        <v>0.05882352941176449</v>
+        <v>0.1176470588235295</v>
       </c>
       <c r="D39" t="n">
         <v>1</v>
       </c>
       <c r="E39" t="n">
-        <v>0.4135472370766486</v>
+        <v>0.4331550802139041</v>
       </c>
     </row>
     <row r="40">
@@ -904,13 +904,13 @@
         <v>0.2272727272727273</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1176470588235295</v>
+        <v>0.176470588235294</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9636404733077018</v>
+        <v>0.9680561565490443</v>
       </c>
       <c r="E40" t="n">
-        <v>0.4361867531346529</v>
+        <v>0.4572664906856885</v>
       </c>
     </row>
     <row r="41">
@@ -923,13 +923,13 @@
         <v>0.2727272727272735</v>
       </c>
       <c r="C41" t="n">
-        <v>0.05882352941176449</v>
+        <v>0.1176470588235295</v>
       </c>
       <c r="D41" t="n">
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4438502673796793</v>
+        <v>0.4634581105169344</v>
       </c>
     </row>
     <row r="42">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.318181818181818</v>
+        <v>0.2727272727272735</v>
       </c>
       <c r="C42" t="n">
         <v>0.1176470588235295</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8324983307105308</v>
+        <v>0.8496519028298313</v>
       </c>
       <c r="E42" t="n">
-        <v>0.4227757359052928</v>
+        <v>0.4133420781268781</v>
       </c>
     </row>
     <row r="43">
@@ -964,10 +964,10 @@
         <v>0.1176470588235295</v>
       </c>
       <c r="D43" t="n">
-        <v>0.8381066921276011</v>
+        <v>0.8545129700067381</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3943421594079526</v>
+        <v>0.3998109187009983</v>
       </c>
     </row>
     <row r="44">
@@ -983,10 +983,10 @@
         <v>0.1176470588235295</v>
       </c>
       <c r="D44" t="n">
-        <v>0.8780267230919101</v>
+        <v>0.8905612560660224</v>
       </c>
       <c r="E44" t="n">
-        <v>0.4076488363960557</v>
+        <v>0.4118270140540931</v>
       </c>
     </row>
     <row r="45">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2727272727272735</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="C45" t="n">
-        <v>0.05882352941176449</v>
+        <v>0.1176470588235295</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7830522467498834</v>
+        <v>0.8049778965668238</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3715343496296404</v>
+        <v>0.3832992275543602</v>
       </c>
     </row>
     <row r="46">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4090909090909086</v>
+        <v>0.4090909090909102</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.6813976143813343</v>
+        <v>0.713339192629582</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3634961744907476</v>
+        <v>0.374143367240164</v>
       </c>
     </row>
     <row r="47">
@@ -1040,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2039315465827464</v>
+        <v>0.2830795797543156</v>
       </c>
       <c r="E47" t="n">
-        <v>0.2649468791639459</v>
+        <v>0.2913295568878023</v>
       </c>
     </row>
     <row r="48">
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8181818181818188</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.4546540657780138</v>
+        <v>0.5088844678235531</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4242786279866109</v>
+        <v>0.4272039135169419</v>
       </c>
     </row>
     <row r="49">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9090909090909094</v>
+        <v>0.8636363636363649</v>
       </c>
       <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0.7578228665631759</v>
+        <v>0.7821129659347716</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5556379252180285</v>
+        <v>0.5485831098570455</v>
       </c>
     </row>
     <row r="50">
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8636363636363633</v>
+        <v>0.8181818181818188</v>
       </c>
       <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.7267048821889011</v>
+        <v>0.7541968664744032</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5301137486084214</v>
+        <v>0.5241262282187407</v>
       </c>
     </row>
     <row r="51">
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9545454545454555</v>
+        <v>0.9090909090909094</v>
       </c>
       <c r="C51" t="n">
         <v>0.04999999999999982</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9191340608899673</v>
+        <v>0.9279450862400527</v>
       </c>
       <c r="E51" t="n">
-        <v>0.6412265051451409</v>
+        <v>0.629011998443654</v>
       </c>
     </row>
     <row r="52">
@@ -1129,16 +1129,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9545454545454555</v>
+        <v>0.9090909090909094</v>
       </c>
       <c r="C52" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9354739862101402</v>
+        <v>0.9427410119443859</v>
       </c>
       <c r="E52" t="n">
-        <v>0.6633398135851986</v>
+        <v>0.6672773070117651</v>
       </c>
     </row>
     <row r="53">
@@ -1151,13 +1151,13 @@
         <v>0.9545454545454555</v>
       </c>
       <c r="C53" t="n">
-        <v>0.04999999999999982</v>
+        <v>0.1000000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>0.9759592328097707</v>
+        <v>0.9794445854035727</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6601682291184087</v>
+        <v>0.6779966799830094</v>
       </c>
     </row>
     <row r="54">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>0.9545454545454555</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8883007681125101</v>
+        <v>0.9008948618122039</v>
       </c>
       <c r="E54" t="n">
-        <v>0.66276692270417</v>
+        <v>0.6684801054525531</v>
       </c>
     </row>
     <row r="55">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1999999999999997</v>
+        <v>0.25</v>
       </c>
       <c r="D55" t="n">
-        <v>0.9681645999882894</v>
+        <v>0.9730946232195287</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7227215333294298</v>
+        <v>0.7410315410731761</v>
       </c>
     </row>
     <row r="56">
@@ -1208,13 +1208,13 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.25</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="D56" t="n">
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.75</v>
+        <v>0.7666666666666666</v>
       </c>
     </row>
     <row r="57">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8400000000000005</v>
+        <v>0.8333333333333326</v>
       </c>
       <c r="C57" t="n">
         <v>0.2999999999999998</v>
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7133333333333335</v>
+        <v>0.7111111111111108</v>
       </c>
     </row>
     <row r="58">
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6400000000000006</v>
+        <v>0.6249999999999994</v>
       </c>
       <c r="C58" t="n">
         <v>0.3999999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9939424386638944</v>
+        <v>0.9947231748960665</v>
       </c>
       <c r="E58" t="n">
-        <v>0.6779808128879651</v>
+        <v>0.6732410582986886</v>
       </c>
     </row>
     <row r="59">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3200000000000003</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C59" t="n">
         <v>0.5</v>
       </c>
       <c r="D59" t="n">
-        <v>0.5793073109953386</v>
+        <v>0.6194851476334481</v>
       </c>
       <c r="E59" t="n">
-        <v>0.4664357703317796</v>
+        <v>0.4842728269889271</v>
       </c>
     </row>
     <row r="60">
@@ -1281,16 +1281,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4400000000000006</v>
+        <v>0.4583333333333335</v>
       </c>
       <c r="C60" t="n">
-        <v>0.5</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="D60" t="n">
-        <v>0.7948635305467961</v>
+        <v>0.814703135677309</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5782878435155989</v>
+        <v>0.6076788230035475</v>
       </c>
     </row>
     <row r="61">
@@ -1300,16 +1300,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4799999999999997</v>
+        <v>0.4999999999999993</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="D61" t="n">
         <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.683333333333333</v>
       </c>
     </row>
     <row r="62">
@@ -1319,16 +1319,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6</v>
+        <v>0.6249999999999994</v>
       </c>
       <c r="C62" t="n">
         <v>0.5</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9725506805246665</v>
+        <v>0.976211959824916</v>
       </c>
       <c r="E62" t="n">
-        <v>0.6908502268415555</v>
+        <v>0.7004039866083053</v>
       </c>
     </row>
     <row r="63">
@@ -1338,16 +1338,16 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6</v>
+        <v>0.6249999999999994</v>
       </c>
       <c r="C63" t="n">
-        <v>0.5</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7249999999999998</v>
       </c>
     </row>
     <row r="64">
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6799999999999997</v>
+        <v>0.7499999999999997</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5499999999999998</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>0.9749943209794701</v>
+        <v>0.9766249935913064</v>
       </c>
       <c r="E64" t="n">
-        <v>0.7349981069931566</v>
+        <v>0.7755416645304353</v>
       </c>
     </row>
     <row r="65">
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7200000000000003</v>
+        <v>0.7499999999999997</v>
       </c>
       <c r="C65" t="n">
         <v>0.5</v>
       </c>
       <c r="D65" t="n">
-        <v>0.9310890047696613</v>
+        <v>0.9413080276142702</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7170296682565538</v>
+        <v>0.7304360092047566</v>
       </c>
     </row>
     <row r="66">
@@ -1395,16 +1395,16 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6400000000000006</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C66" t="n">
-        <v>0.5</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="D66" t="n">
-        <v>0.8532586043753161</v>
+        <v>0.8704106420610767</v>
       </c>
       <c r="E66" t="n">
-        <v>0.6644195347917722</v>
+        <v>0.6956924362425809</v>
       </c>
     </row>
     <row r="67">
@@ -1414,16 +1414,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6400000000000006</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C67" t="n">
-        <v>0.5</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="D67" t="n">
-        <v>0.8022453519074121</v>
+        <v>0.8236933452801616</v>
       </c>
       <c r="E67" t="n">
-        <v>0.6474151173024709</v>
+        <v>0.680120003982276</v>
       </c>
     </row>
     <row r="68">
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6400000000000006</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="C68" t="n">
-        <v>0.5</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="D68" t="n">
-        <v>0.8474426356083036</v>
+        <v>0.8656792718241696</v>
       </c>
       <c r="E68" t="n">
-        <v>0.6624808785361014</v>
+        <v>0.6941153128302786</v>
       </c>
     </row>
     <row r="69">
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6</v>
+        <v>0.6249999999999994</v>
       </c>
       <c r="C69" t="n">
         <v>0.5</v>
       </c>
       <c r="D69" t="n">
-        <v>0.8158990546782403</v>
+        <v>0.8375821687703922</v>
       </c>
       <c r="E69" t="n">
-        <v>0.6386330182260801</v>
+        <v>0.6541940562567973</v>
       </c>
     </row>
     <row r="70">
@@ -1471,16 +1471,16 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5200000000000002</v>
+        <v>0.5833333333333337</v>
       </c>
       <c r="C70" t="n">
-        <v>0.4499999999999997</v>
+        <v>0.5</v>
       </c>
       <c r="D70" t="n">
-        <v>0.656285574365805</v>
+        <v>0.6917450670248385</v>
       </c>
       <c r="E70" t="n">
-        <v>0.5420951914552683</v>
+        <v>0.5916928001193907</v>
       </c>
     </row>
     <row r="71">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4</v>
+        <v>0.4166666666666663</v>
       </c>
       <c r="C71" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.4499999999999997</v>
       </c>
       <c r="D71" t="n">
-        <v>0.1978798745881518</v>
+        <v>0.2724702528146602</v>
       </c>
       <c r="E71" t="n">
-        <v>0.3326266248627173</v>
+        <v>0.3797123064937755</v>
       </c>
     </row>
     <row r="72">
@@ -1509,16 +1509,16 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.3599999999999994</v>
+        <v>0.4166666666666663</v>
       </c>
       <c r="C72" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.4499999999999997</v>
       </c>
       <c r="D72" t="n">
-        <v>0.3383638932231869</v>
+        <v>0.4014108069632996</v>
       </c>
       <c r="E72" t="n">
-        <v>0.3661212977410621</v>
+        <v>0.4226924912099885</v>
       </c>
     </row>
     <row r="73">
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.3200000000000003</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="C73" t="n">
-        <v>0.3500000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>0.4568692169531141</v>
+        <v>0.5102113018006617</v>
       </c>
       <c r="E73" t="n">
-        <v>0.3756230723177048</v>
+        <v>0.4145148783779982</v>
       </c>
     </row>
     <row r="74">
@@ -1547,16 +1547,16 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.2799999999999997</v>
+        <v>0.2916666666666661</v>
       </c>
       <c r="C74" t="n">
-        <v>0.3500000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="D74" t="n">
-        <v>0.3628231483643701</v>
+        <v>0.424598883606307</v>
       </c>
       <c r="E74" t="n">
-        <v>0.33094104945479</v>
+        <v>0.3720885167576577</v>
       </c>
     </row>
     <row r="75">
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.1200000000000003</v>
+        <v>0.1250000000000002</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2999999999999998</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="D75" t="n">
-        <v>0.4356421767454646</v>
+        <v>0.4917212815545563</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2852140589151549</v>
+        <v>0.3222404271848522</v>
       </c>
     </row>
     <row r="76">
@@ -1588,13 +1588,13 @@
         <v>0</v>
       </c>
       <c r="C76" t="n">
-        <v>0.3500000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="D76" t="n">
-        <v>0.390009431026839</v>
+        <v>0.4561832144991673</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2466698103422797</v>
+        <v>0.2853944048330557</v>
       </c>
     </row>
     <row r="77">
@@ -1607,13 +1607,13 @@
         <v>0</v>
       </c>
       <c r="C77" t="n">
-        <v>0.25</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="D77" t="n">
-        <v>0.3112272615118404</v>
+        <v>0.3843416404621943</v>
       </c>
       <c r="E77" t="n">
-        <v>0.1870757538372801</v>
+        <v>0.2281138801540647</v>
       </c>
     </row>
     <row r="78">
@@ -1623,16 +1623,16 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.1111111111111114</v>
+        <v>0.04166666666666722</v>
       </c>
       <c r="C78" t="n">
-        <v>0.25</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2399283557599176</v>
+        <v>0.3187939095792203</v>
       </c>
       <c r="E78" t="n">
-        <v>0.2003464889570097</v>
+        <v>0.2201535254152958</v>
       </c>
     </row>
     <row r="79">
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.2222222222222215</v>
+        <v>0.2083333333333331</v>
       </c>
       <c r="C79" t="n">
-        <v>0.25</v>
+        <v>0.2999999999999998</v>
       </c>
       <c r="D79" t="n">
-        <v>0.1629527256875273</v>
+        <v>0.2479810814968522</v>
       </c>
       <c r="E79" t="n">
-        <v>0.2117249826365829</v>
+        <v>0.2521048049433951</v>
       </c>
     </row>
     <row r="80">
@@ -1661,16 +1661,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.2962962962962966</v>
+        <v>0.2500000000000004</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1999999999999997</v>
+        <v>0.25</v>
       </c>
       <c r="D80" t="n">
-        <v>0.1102481552651509</v>
+        <v>0.1974502257562492</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2021814838538158</v>
+        <v>0.2324834085854165</v>
       </c>
     </row>
     <row r="81">
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.1851851851851852</v>
+        <v>0.1666666666666674</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1499999999999999</v>
+        <v>0.1999999999999997</v>
       </c>
       <c r="D81" t="n">
-        <v>0.112324365126543</v>
+        <v>0.1990704171206821</v>
       </c>
       <c r="E81" t="n">
-        <v>0.1491698501039094</v>
+        <v>0.1885790279291164</v>
       </c>
     </row>
     <row r="82">
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.1111111111111114</v>
+        <v>0.04166666666666722</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1000000000000001</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>0.09469954379412228</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0703703703703705</v>
+        <v>0.09545540348692981</v>
       </c>
     </row>
     <row r="83">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.03703703703703626</v>
+        <v>0</v>
       </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0.01234567901234542</v>
+        <v>0.01666666666666661</v>
       </c>
     </row>
     <row r="84">
@@ -1740,13 +1740,13 @@
         <v>0</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>0.04999999999999982</v>
       </c>
       <c r="D84" t="n">
-        <v>0.07217268456268752</v>
+        <v>0.0919668901002043</v>
       </c>
       <c r="E84" t="n">
-        <v>0.02405756152089584</v>
+        <v>0.04732229670006805</v>
       </c>
     </row>
     <row r="85">
@@ -1762,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.2373397296057668</v>
+        <v>0.2606429582478396</v>
       </c>
       <c r="E85" t="n">
-        <v>0.07911324320192227</v>
+        <v>0.08688098608261319</v>
       </c>
     </row>
     <row r="86">
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.03571428571428621</v>
+        <v>0.03703703703703753</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.1736702105847082</v>
+        <v>0.1986749147155459</v>
       </c>
       <c r="E86" t="n">
-        <v>0.06979483209966479</v>
+        <v>0.07857065058419449</v>
       </c>
     </row>
     <row r="87">
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.1428571428571436</v>
+        <v>0.1111111111111113</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.207998181465494</v>
+        <v>0.2344603022598383</v>
       </c>
       <c r="E87" t="n">
-        <v>0.1169517747742125</v>
+        <v>0.1151904711236498</v>
       </c>
     </row>
     <row r="88">
@@ -1813,16 +1813,16 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.2499999999999997</v>
+        <v>0.2222222222222225</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.1512087838932729</v>
+        <v>0.1789173120196445</v>
       </c>
       <c r="E88" t="n">
-        <v>0.1337362612977575</v>
+        <v>0.1337131780806223</v>
       </c>
     </row>
     <row r="89">
@@ -1832,16 +1832,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.3214285714285721</v>
+        <v>0.37037037037037</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.175105132324621</v>
+        <v>0.2052644274097824</v>
       </c>
       <c r="E89" t="n">
-        <v>0.1655112345843977</v>
+        <v>0.1918782659267174</v>
       </c>
     </row>
     <row r="90">
@@ -1851,16 +1851,16 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.2142857142857147</v>
+        <v>0.185185185185185</v>
       </c>
       <c r="C90" t="n">
-        <v>0.04347826086956506</v>
+        <v>0.04545454545454529</v>
       </c>
       <c r="D90" t="n">
-        <v>0.09045990357805485</v>
+        <v>0.1213751722158816</v>
       </c>
       <c r="E90" t="n">
-        <v>0.1160746262444449</v>
+        <v>0.1173383009518706</v>
       </c>
     </row>
     <row r="91">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1071428571428574</v>
+        <v>0.07407407407407506</v>
       </c>
       <c r="C91" t="n">
-        <v>0.04347826086956506</v>
+        <v>0.04545454545454529</v>
       </c>
       <c r="D91" t="n">
-        <v>0.03831298161070876</v>
+        <v>0.06988382567382279</v>
       </c>
       <c r="E91" t="n">
-        <v>0.06297803320771041</v>
+        <v>0.06313748173414771</v>
       </c>
     </row>
     <row r="92">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.1428571428571436</v>
+        <v>0.1111111111111113</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.01791067967242742</v>
+        <v>0.05070704636073997</v>
       </c>
       <c r="E92" t="n">
-        <v>0.05358927417652367</v>
+        <v>0.05393938582395041</v>
       </c>
     </row>
     <row r="93">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.1071428571428574</v>
+        <v>0.1111111111111113</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.04898742351801629</v>
+        <v>0.08470716949469945</v>
       </c>
       <c r="E93" t="n">
-        <v>0.05204342688695789</v>
+        <v>0.0652727602019369</v>
       </c>
     </row>
     <row r="94">
@@ -1927,16 +1927,16 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.1785714285714285</v>
+        <v>0.1481481481481488</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0.006163490244665353</v>
+        <v>0.01775627016430798</v>
       </c>
       <c r="E94" t="n">
-        <v>0.06157830627203129</v>
+        <v>0.05530147277081892</v>
       </c>
     </row>
     <row r="95">
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2857142857142859</v>
+        <v>0.25925925925926</v>
       </c>
       <c r="C95" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0.0952380952380953</v>
+        <v>0.08641975308642001</v>
       </c>
     </row>
     <row r="96">
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.3214285714285721</v>
+        <v>0.3333333333333338</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.1239804710481171</v>
+        <v>0.1274114744239928</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1484696808255631</v>
+        <v>0.1535816025857755</v>
       </c>
     </row>
     <row r="97">
@@ -1984,16 +1984,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.3928571428571432</v>
+        <v>0.4074074074074075</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2448778821631855</v>
+        <v>0.251827182758644</v>
       </c>
       <c r="E97" t="n">
-        <v>0.2125783416734429</v>
+        <v>0.2197448633886838</v>
       </c>
     </row>
     <row r="98">
@@ -2003,16 +2003,16 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.3928571428571432</v>
+        <v>0.4074074074074075</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2320166827458945</v>
+        <v>0.2403322312375094</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2082912752010126</v>
+        <v>0.215913212881639</v>
       </c>
     </row>
     <row r="99">
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5714285714285718</v>
+        <v>0.5925925925925924</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2854673416493079</v>
+        <v>0.2958785670844841</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2856319710259599</v>
+        <v>0.2961570532256922</v>
       </c>
     </row>
     <row r="100">
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6785714285714292</v>
+        <v>0.7407407407407399</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03999999999999986</v>
+        <v>0.04166666666666688</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2905293572727042</v>
+        <v>0.3019317271839393</v>
       </c>
       <c r="E100" t="n">
-        <v>0.3363669286147111</v>
+        <v>0.3614463781971153</v>
       </c>
     </row>
     <row r="101">
@@ -2063,13 +2063,13 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0.03999999999999986</v>
+        <v>0.04166666666666688</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3513175817075109</v>
+        <v>0.3650606198010092</v>
       </c>
       <c r="E101" t="n">
-        <v>0.4637725272358369</v>
+        <v>0.4689090954892254</v>
       </c>
     </row>
     <row r="102">
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.8999999999999998</v>
+        <v>0.8749999999999994</v>
       </c>
       <c r="C102" t="n">
-        <v>0.03999999999999986</v>
+        <v>0.04166666666666688</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2860368403049701</v>
+        <v>0.2989804724093655</v>
       </c>
       <c r="E102" t="n">
-        <v>0.4086789467683232</v>
+        <v>0.4052157130253439</v>
       </c>
     </row>
     <row r="103">
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.9333333333333336</v>
+        <v>0.8749999999999994</v>
       </c>
       <c r="C103" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.04166666666666688</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2805459391879865</v>
+        <v>0.2942301618472238</v>
       </c>
       <c r="E103" t="n">
-        <v>0.43129309084044</v>
+        <v>0.4036322761712967</v>
       </c>
     </row>
     <row r="104">
@@ -2117,16 +2117,16 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6249999999999994</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1199999999999999</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2809435606936265</v>
+        <v>0.2955600487797549</v>
       </c>
       <c r="E104" t="n">
-        <v>0.3558700757867643</v>
+        <v>0.3485200162599181</v>
       </c>
     </row>
     <row r="105">
@@ -2136,16 +2136,16 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5666666666666664</v>
+        <v>0.5</v>
       </c>
       <c r="C105" t="n">
-        <v>0.1199999999999999</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="D105" t="n">
-        <v>0.240231352345476</v>
+        <v>0.2544007488826512</v>
       </c>
       <c r="E105" t="n">
-        <v>0.3089660063373807</v>
+        <v>0.2931335829608837</v>
       </c>
     </row>
     <row r="106">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.3999999999999997</v>
+        <v>0.3437500000000001</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1199999999999999</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="D106" t="n">
-        <v>0.1981927225528276</v>
+        <v>0.210876468714607</v>
       </c>
       <c r="E106" t="n">
-        <v>0.2393975741842758</v>
+        <v>0.2265421562382023</v>
       </c>
     </row>
     <row r="107">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.2666666666666669</v>
+        <v>0.2187500000000007</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1199999999999999</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="D107" t="n">
-        <v>0.02479784971327119</v>
+        <v>0.03320867850220396</v>
       </c>
       <c r="E107" t="n">
-        <v>0.1371548387933127</v>
+        <v>0.1256528928340682</v>
       </c>
     </row>
     <row r="108">
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.2666666666666669</v>
+        <v>0.2187500000000007</v>
       </c>
       <c r="C108" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.0833333333333334</v>
       </c>
       <c r="D108" t="n">
-        <v>0.1035980211576326</v>
+        <v>0.1143472688322961</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1500882292747665</v>
+        <v>0.1388102007218767</v>
       </c>
     </row>
     <row r="109">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.2333333333333331</v>
+        <v>0.2187500000000007</v>
       </c>
       <c r="C109" t="n">
-        <v>0.1599999999999998</v>
+        <v>0.1666666666666668</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2048299465559415</v>
+        <v>0.2186032841721531</v>
       </c>
       <c r="E109" t="n">
-        <v>0.1993877599630914</v>
+        <v>0.2013399836129402</v>
       </c>
     </row>
     <row r="110">
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5666666666666664</v>
+        <v>0.5624999999999998</v>
       </c>
       <c r="C110" t="n">
-        <v>0.2</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="D110" t="n">
-        <v>0.2451654173843092</v>
+        <v>0.2608852353232828</v>
       </c>
       <c r="E110" t="n">
-        <v>0.3372773613503252</v>
+        <v>0.3439061895522053</v>
       </c>
     </row>
     <row r="111">
@@ -2250,16 +2250,16 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.3999999999999997</v>
+        <v>0.4062499999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>0.32</v>
+        <v>0.3333333333333332</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4283229775251577</v>
+        <v>0.4496545779210505</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3827743258417192</v>
+        <v>0.3964126370847945</v>
       </c>
     </row>
     <row r="112">
@@ -2272,13 +2272,13 @@
         <v>0</v>
       </c>
       <c r="C112" t="n">
-        <v>0.3599999999999998</v>
+        <v>0.3750000000000001</v>
       </c>
       <c r="D112" t="n">
-        <v>0.3165758112709071</v>
+        <v>0.3358003984846665</v>
       </c>
       <c r="E112" t="n">
-        <v>0.2255252704236356</v>
+        <v>0.2369334661615556</v>
       </c>
     </row>
     <row r="113">
@@ -2291,13 +2291,13 @@
         <v>0</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2399999999999999</v>
+        <v>0.2500000000000002</v>
       </c>
       <c r="D113" t="n">
-        <v>0.1678060787477241</v>
+        <v>0.1839690628946757</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1359353595825747</v>
+        <v>0.1446563542982253</v>
       </c>
     </row>
     <row r="114">
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="C114" t="n">
-        <v>0.1599999999999998</v>
+        <v>0.1666666666666668</v>
       </c>
       <c r="D114" t="n">
-        <v>0.01685373950402727</v>
+        <v>0.02988643543015799</v>
       </c>
       <c r="E114" t="n">
-        <v>0.05895124650134235</v>
+        <v>0.0655177006989416</v>
       </c>
     </row>
     <row r="115">
@@ -2329,13 +2329,13 @@
         <v>0</v>
       </c>
       <c r="C115" t="n">
-        <v>0.08000000000000007</v>
+        <v>0.04166666666666688</v>
       </c>
       <c r="D115" t="n">
         <v>0</v>
       </c>
       <c r="E115" t="n">
-        <v>0.02666666666666669</v>
+        <v>0.01388888888888896</v>
       </c>
     </row>
     <row r="116">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.05882352941176417</v>
+        <v>0.03773584905660363</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="E116" t="n">
-        <v>0.01960784313725472</v>
+        <v>0.01257861635220121</v>
       </c>
     </row>
     <row r="117">
@@ -2364,7 +2364,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.1764705882352939</v>
+        <v>0.1320754716981131</v>
       </c>
       <c r="C117" t="n">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="E117" t="n">
-        <v>0.05882352941176464</v>
+        <v>0.04402515723270436</v>
       </c>
     </row>
     <row r="118">
@@ -2383,7 +2383,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.2830188679245282</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -2392,7 +2392,7 @@
         <v>0</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09433962264150941</v>
       </c>
     </row>
     <row r="119">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.3773584905660377</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
@@ -2411,7 +2411,7 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1568627450980392</v>
+        <v>0.1257861635220126</v>
       </c>
     </row>
     <row r="120">
@@ -2421,16 +2421,16 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5098039215686272</v>
+        <v>0.452830188679245</v>
       </c>
       <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0805288853959235</v>
+        <v>0.08432386816264849</v>
       </c>
       <c r="E120" t="n">
-        <v>0.1967776023215169</v>
+        <v>0.1790513522806312</v>
       </c>
     </row>
     <row r="121">
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4705882352941176</v>
+        <v>0.4150943396226413</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1731136246738035</v>
+        <v>0.1797646780629271</v>
       </c>
       <c r="E121" t="n">
-        <v>0.2145672866559737</v>
+        <v>0.1982863392285228</v>
       </c>
     </row>
     <row r="122">
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5294117647058825</v>
+        <v>0.4716981132075471</v>
       </c>
       <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0.2153533575103212</v>
+        <v>0.222881401686199</v>
       </c>
       <c r="E122" t="n">
-        <v>0.2482550407387346</v>
+        <v>0.231526504964582</v>
       </c>
     </row>
     <row r="123">
@@ -2478,16 +2478,16 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5294117647058825</v>
+        <v>0.4905660377358486</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>0.2485604032823319</v>
+        <v>0.2578785365837941</v>
       </c>
       <c r="E123" t="n">
-        <v>0.2593240559960715</v>
+        <v>0.2494815247732142</v>
       </c>
     </row>
     <row r="124">
@@ -2497,16 +2497,16 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6078431372549018</v>
+        <v>0.5660377358490565</v>
       </c>
       <c r="C124" t="n">
-        <v>0.03124999999999989</v>
+        <v>0.0322580645161292</v>
       </c>
       <c r="D124" t="n">
-        <v>0.2545599775084994</v>
+        <v>0.2621361910098082</v>
       </c>
       <c r="E124" t="n">
-        <v>0.2978843715878003</v>
+        <v>0.2868106637916646</v>
       </c>
     </row>
     <row r="125">
@@ -2516,16 +2516,16 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.627450980392157</v>
+        <v>0.6037735849056601</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.2814720600383868</v>
+        <v>0.2912782721622858</v>
       </c>
       <c r="E125" t="n">
-        <v>0.3029743468101813</v>
+        <v>0.2983506190226486</v>
       </c>
     </row>
     <row r="126">
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.7058823529411763</v>
+        <v>0.660377358490566</v>
       </c>
       <c r="C126" t="n">
-        <v>0.03124999999999989</v>
+        <v>0.0322580645161292</v>
       </c>
       <c r="D126" t="n">
-        <v>0.2878714351788128</v>
+        <v>0.3010636222012054</v>
       </c>
       <c r="E126" t="n">
-        <v>0.3416679293733296</v>
+        <v>0.3312330150693002</v>
       </c>
     </row>
     <row r="127">
@@ -2554,16 +2554,16 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.7843137254901964</v>
+        <v>0.7169811320754718</v>
       </c>
       <c r="C127" t="n">
-        <v>0.03124999999999989</v>
+        <v>0.0322580645161292</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3567797887508668</v>
+        <v>0.3704465919714397</v>
       </c>
       <c r="E127" t="n">
-        <v>0.3907811714136877</v>
+        <v>0.3732285961876802</v>
       </c>
     </row>
     <row r="128">
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.9607843137254903</v>
+        <v>0.8867924528301884</v>
       </c>
       <c r="C128" t="n">
-        <v>0.06250000000000006</v>
+        <v>0.0645161290322581</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4338893293994195</v>
+        <v>0.4501251535328989</v>
       </c>
       <c r="E128" t="n">
-        <v>0.4857245477083033</v>
+        <v>0.4671445784651151</v>
       </c>
     </row>
     <row r="129">
@@ -2595,13 +2595,13 @@
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>0.06250000000000006</v>
+        <v>0.0645161290322581</v>
       </c>
       <c r="D129" t="n">
-        <v>0.5109885971651589</v>
+        <v>0.529685447230225</v>
       </c>
       <c r="E129" t="n">
-        <v>0.524496199055053</v>
+        <v>0.5314005254208277</v>
       </c>
     </row>
     <row r="130">
@@ -2614,13 +2614,13 @@
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0.09374999999999994</v>
+        <v>0.0645161290322581</v>
       </c>
       <c r="D130" t="n">
-        <v>0.5224447035496396</v>
+        <v>0.5410085340371137</v>
       </c>
       <c r="E130" t="n">
-        <v>0.5387315678498799</v>
+        <v>0.5351748876897906</v>
       </c>
     </row>
     <row r="131">
@@ -2633,13 +2633,13 @@
         <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>0.1250000000000001</v>
+        <v>0.09677419354838732</v>
       </c>
       <c r="D131" t="n">
-        <v>0.5136450353772372</v>
+        <v>0.5304280387025574</v>
       </c>
       <c r="E131" t="n">
-        <v>0.5462150117924124</v>
+        <v>0.5424007440836482</v>
       </c>
     </row>
     <row r="132">
@@ -2652,13 +2652,13 @@
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>0.1874999999999999</v>
+        <v>0.1935483870967743</v>
       </c>
       <c r="D132" t="n">
-        <v>0.6897536986809645</v>
+        <v>0.712021342487658</v>
       </c>
       <c r="E132" t="n">
-        <v>0.6257512328936549</v>
+        <v>0.6351899098614774</v>
       </c>
     </row>
     <row r="133">
@@ -2668,16 +2668,16 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.9242424242424242</v>
+        <v>0.9354838709677421</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2187500000000001</v>
+        <v>0.2258064516129032</v>
       </c>
       <c r="D133" t="n">
-        <v>0.7999634422509253</v>
+        <v>0.8232897008055995</v>
       </c>
       <c r="E133" t="n">
-        <v>0.6476519554977832</v>
+        <v>0.6615266744620817</v>
       </c>
     </row>
     <row r="134">
@@ -2687,16 +2687,16 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.8787878787878787</v>
+        <v>0.9032258064516127</v>
       </c>
       <c r="C134" t="n">
-        <v>0.2499999999999999</v>
+        <v>0.2580645161290324</v>
       </c>
       <c r="D134" t="n">
-        <v>0.8069652104845713</v>
+        <v>0.8324649346273065</v>
       </c>
       <c r="E134" t="n">
-        <v>0.6452510297574833</v>
+        <v>0.6645850857359838</v>
       </c>
     </row>
     <row r="135">
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.893939393939394</v>
+        <v>0.9354838709677421</v>
       </c>
       <c r="C135" t="n">
-        <v>0.3125</v>
+        <v>0.3225806451612903</v>
       </c>
       <c r="D135" t="n">
-        <v>0.830376250781286</v>
+        <v>0.8567918560870487</v>
       </c>
       <c r="E135" t="n">
-        <v>0.6789385482402267</v>
+        <v>0.704952124072027</v>
       </c>
     </row>
     <row r="136">
@@ -2725,16 +2725,16 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.8636363636363638</v>
+        <v>0.9032258064516127</v>
       </c>
       <c r="C136" t="n">
-        <v>0.4062499999999999</v>
+        <v>0.4193548387096776</v>
       </c>
       <c r="D136" t="n">
-        <v>0.8427303504385472</v>
+        <v>0.8694618519767494</v>
       </c>
       <c r="E136" t="n">
-        <v>0.7042055713583036</v>
+        <v>0.7306808323793467</v>
       </c>
     </row>
     <row r="137">
@@ -2744,16 +2744,16 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.9545454545454545</v>
+        <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0.3750000000000001</v>
+        <v>0.3870967741935484</v>
       </c>
       <c r="D137" t="n">
-        <v>0.8621984129111688</v>
+        <v>0.89261006526663</v>
       </c>
       <c r="E137" t="n">
-        <v>0.7305812891522079</v>
+        <v>0.7599022798200595</v>
       </c>
     </row>
     <row r="138">
@@ -2766,13 +2766,13 @@
         <v>1</v>
       </c>
       <c r="C138" t="n">
-        <v>0.46875</v>
+        <v>0.4838709677419354</v>
       </c>
       <c r="D138" t="n">
-        <v>0.8770984108158376</v>
+        <v>0.9081061978823698</v>
       </c>
       <c r="E138" t="n">
-        <v>0.7819494702719458</v>
+        <v>0.7973257218747684</v>
       </c>
     </row>
     <row r="139">
@@ -2785,13 +2785,13 @@
         <v>1</v>
       </c>
       <c r="C139" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D139" t="n">
-        <v>0.8809130086054372</v>
+        <v>0.9115653228019891</v>
       </c>
       <c r="E139" t="n">
-        <v>0.7936376695351458</v>
+        <v>0.8092314516866845</v>
       </c>
     </row>
     <row r="140">
@@ -2804,13 +2804,13 @@
         <v>1</v>
       </c>
       <c r="C140" t="n">
-        <v>0.53125</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="D140" t="n">
-        <v>0.931558621879114</v>
+        <v>0.9618217250861214</v>
       </c>
       <c r="E140" t="n">
-        <v>0.820936207293038</v>
+        <v>0.8367362739534383</v>
       </c>
     </row>
     <row r="141">
@@ -2823,13 +2823,13 @@
         <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>0.5624999999999999</v>
+        <v>0.5806451612903227</v>
       </c>
       <c r="D141" t="n">
-        <v>0.9434585701441283</v>
+        <v>0.9760134220462652</v>
       </c>
       <c r="E141" t="n">
-        <v>0.8353195233813761</v>
+        <v>0.8522195277788627</v>
       </c>
     </row>
     <row r="142">
@@ -2842,13 +2842,13 @@
         <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>0.5624999999999999</v>
+        <v>0.5806451612903227</v>
       </c>
       <c r="D142" t="n">
-        <v>0.9341003903548799</v>
+        <v>0.9663459569184722</v>
       </c>
       <c r="E142" t="n">
-        <v>0.8322001301182933</v>
+        <v>0.8489970394029317</v>
       </c>
     </row>
     <row r="143">
@@ -2861,13 +2861,13 @@
         <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>0.5937500000000001</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="D143" t="n">
-        <v>0.8843984889000329</v>
+        <v>0.9118676661595573</v>
       </c>
       <c r="E143" t="n">
-        <v>0.826049496300011</v>
+        <v>0.841590297322003</v>
       </c>
     </row>
     <row r="144">
@@ -2880,13 +2880,13 @@
         <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.6562499999999999</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="D144" t="n">
-        <v>0.9359548364085427</v>
+        <v>0.9645308291811198</v>
       </c>
       <c r="E144" t="n">
-        <v>0.8640682788028475</v>
+        <v>0.8806500613399432</v>
       </c>
     </row>
     <row r="145">
@@ -2899,13 +2899,13 @@
         <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>0.6562499999999999</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="D145" t="n">
         <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>0.8854166666666666</v>
+        <v>0.89247311827957</v>
       </c>
     </row>
     <row r="146">
@@ -2918,13 +2918,13 @@
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0.6562499999999999</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="D146" t="n">
-        <v>0.9534504164253911</v>
+        <v>0.9536012688232502</v>
       </c>
       <c r="E146" t="n">
-        <v>0.8699001388084637</v>
+        <v>0.8770068745539866</v>
       </c>
     </row>
     <row r="147">
@@ -2937,13 +2937,13 @@
         <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>0.6875</v>
+        <v>0.7096774193548386</v>
       </c>
       <c r="D147" t="n">
         <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>0.8958333333333334</v>
+        <v>0.9032258064516129</v>
       </c>
     </row>
     <row r="148">
@@ -2956,13 +2956,13 @@
         <v>1</v>
       </c>
       <c r="C148" t="n">
-        <v>0.7187499999999999</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="D148" t="n">
-        <v>0.987505664722233</v>
+        <v>0.9870362672921551</v>
       </c>
       <c r="E148" t="n">
-        <v>0.9020852215740777</v>
+        <v>0.9204099385597506</v>
       </c>
     </row>
     <row r="149">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.9759036144578314</v>
+        <v>0.9756097560975611</v>
       </c>
       <c r="C149" t="n">
-        <v>0.7187499999999999</v>
+        <v>0.7419354838709679</v>
       </c>
       <c r="D149" t="n">
-        <v>0.9393289520615268</v>
+        <v>0.9400328488618431</v>
       </c>
       <c r="E149" t="n">
-        <v>0.8779941888397861</v>
+        <v>0.8858593629434574</v>
       </c>
     </row>
     <row r="150">
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.9277108433734942</v>
+        <v>0.9146341463414634</v>
       </c>
       <c r="C150" t="n">
-        <v>0.6875</v>
+        <v>0.7096774193548386</v>
       </c>
       <c r="D150" t="n">
-        <v>0.8980319984299239</v>
+        <v>0.8992342954046627</v>
       </c>
       <c r="E150" t="n">
-        <v>0.8377476139344727</v>
+        <v>0.8411819537003216</v>
       </c>
     </row>
     <row r="151">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.8674698795180725</v>
+        <v>0.8658536585365851</v>
       </c>
       <c r="C151" t="n">
-        <v>0.6562499999999999</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="D151" t="n">
-        <v>0.9045886593715887</v>
+        <v>0.905661888760471</v>
       </c>
       <c r="E151" t="n">
-        <v>0.8094361796298871</v>
+        <v>0.8163116340452552</v>
       </c>
     </row>
     <row r="152">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.8674698795180725</v>
+        <v>0.8536585365853659</v>
       </c>
       <c r="C152" t="n">
-        <v>0.5937500000000001</v>
+        <v>0.6451612903225805</v>
       </c>
       <c r="D152" t="n">
-        <v>0.8661546337663836</v>
+        <v>0.8676545073159999</v>
       </c>
       <c r="E152" t="n">
-        <v>0.775791504428152</v>
+        <v>0.7888247780746488</v>
       </c>
     </row>
     <row r="153">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.8795180722891566</v>
+        <v>0.8536585365853659</v>
       </c>
       <c r="C153" t="n">
-        <v>0.5937500000000001</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="D153" t="n">
-        <v>0.8761468399010029</v>
+        <v>0.8776942275584794</v>
       </c>
       <c r="E153" t="n">
-        <v>0.7831383040633866</v>
+        <v>0.7814186633167658</v>
       </c>
     </row>
     <row r="154">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.8313253012048194</v>
+        <v>0.8170731707317073</v>
       </c>
       <c r="C154" t="n">
-        <v>0.5624999999999999</v>
+        <v>0.5806451612903227</v>
       </c>
       <c r="D154" t="n">
-        <v>0.859444743363083</v>
+        <v>0.8610748614383315</v>
       </c>
       <c r="E154" t="n">
-        <v>0.7510900148559675</v>
+        <v>0.7529310644867871</v>
       </c>
     </row>
     <row r="155">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.7469879518072291</v>
+        <v>0.7317073170731708</v>
       </c>
       <c r="C155" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D155" t="n">
-        <v>0.7627466073622781</v>
+        <v>0.7649517439682593</v>
       </c>
       <c r="E155" t="n">
-        <v>0.669911519723169</v>
+        <v>0.670929364433165</v>
       </c>
     </row>
     <row r="156">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.7349397590361446</v>
+        <v>0.7195121951219511</v>
       </c>
       <c r="C156" t="n">
-        <v>0.46875</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D156" t="n">
-        <v>0.8528105103443798</v>
+        <v>0.8546303861228126</v>
       </c>
       <c r="E156" t="n">
-        <v>0.6855000897935081</v>
+        <v>0.6967572045009428</v>
       </c>
     </row>
     <row r="157">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.7349397590361446</v>
+        <v>0.7317073170731708</v>
       </c>
       <c r="C157" t="n">
-        <v>0.46875</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D157" t="n">
-        <v>0.927261555634034</v>
+        <v>0.9286928511987693</v>
       </c>
       <c r="E157" t="n">
-        <v>0.7103171048900595</v>
+        <v>0.7255097335100015</v>
       </c>
     </row>
     <row r="158">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.7590361445783131</v>
+        <v>0.7682926829268294</v>
       </c>
       <c r="C158" t="n">
-        <v>0.4375000000000001</v>
+        <v>0.4838709677419354</v>
       </c>
       <c r="D158" t="n">
-        <v>0.9624577434575494</v>
+        <v>0.9308507343731816</v>
       </c>
       <c r="E158" t="n">
-        <v>0.7196646293452876</v>
+        <v>0.7276714616806488</v>
       </c>
     </row>
     <row r="159">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.7710843373493976</v>
+        <v>0.7682926829268294</v>
       </c>
       <c r="C159" t="n">
-        <v>0.46875</v>
+        <v>0.4838709677419354</v>
       </c>
       <c r="D159" t="n">
-        <v>0.9710731241272009</v>
+        <v>0.9394464189797158</v>
       </c>
       <c r="E159" t="n">
-        <v>0.7369691538255329</v>
+        <v>0.7305366898828268</v>
       </c>
     </row>
     <row r="160">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.7710843373493976</v>
+        <v>0.7560975609756098</v>
       </c>
       <c r="C160" t="n">
-        <v>0.46875</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D160" t="n">
-        <v>0.9526198528080617</v>
+        <v>0.9253709050813183</v>
       </c>
       <c r="E160" t="n">
-        <v>0.7308180633858198</v>
+        <v>0.732532499438331</v>
       </c>
     </row>
     <row r="161">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.8072289156626508</v>
+        <v>0.8048780487804876</v>
       </c>
       <c r="C161" t="n">
-        <v>0.4375000000000001</v>
+        <v>0.4838709677419354</v>
       </c>
       <c r="D161" t="n">
-        <v>0.9347747781531663</v>
+        <v>0.9033261872580214</v>
       </c>
       <c r="E161" t="n">
-        <v>0.7265012312719391</v>
+        <v>0.7306917345934815</v>
       </c>
     </row>
     <row r="162">
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.8313253012048194</v>
+        <v>0.8170731707317073</v>
       </c>
       <c r="C162" t="n">
-        <v>0.46875</v>
+        <v>0.4838709677419354</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9185303003362743</v>
+        <v>0.8878202834579203</v>
       </c>
       <c r="E162" t="n">
-        <v>0.7395352005136978</v>
+        <v>0.7295881406438544</v>
       </c>
     </row>
     <row r="163">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.8674698795180725</v>
+        <v>0.8414634146341462</v>
       </c>
       <c r="C163" t="n">
-        <v>0.46875</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D163" t="n">
-        <v>0.9405333228759577</v>
+        <v>0.9089182446586339</v>
       </c>
       <c r="E163" t="n">
-        <v>0.7589177341313434</v>
+        <v>0.7555035638502815</v>
       </c>
     </row>
     <row r="164">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.855421686746988</v>
+        <v>0.8170731707317073</v>
       </c>
       <c r="C164" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D164" t="n">
-        <v>0.9823322045432281</v>
+        <v>0.950550637770796</v>
       </c>
       <c r="E164" t="n">
-        <v>0.7792512970967387</v>
+        <v>0.7612509469201892</v>
       </c>
     </row>
     <row r="165">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.855421686746988</v>
+        <v>0.8048780487804876</v>
       </c>
       <c r="C165" t="n">
-        <v>0.4375000000000001</v>
+        <v>0.4838709677419354</v>
       </c>
       <c r="D165" t="n">
-        <v>0.9844349745515915</v>
+        <v>0.9523360219468819</v>
       </c>
       <c r="E165" t="n">
-        <v>0.7591188870995266</v>
+        <v>0.747028346156435</v>
       </c>
     </row>
     <row r="166">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.8433734939759039</v>
+        <v>0.8048780487804876</v>
       </c>
       <c r="C166" t="n">
-        <v>0.4062499999999999</v>
+        <v>0.4516129032258065</v>
       </c>
       <c r="D166" t="n">
-        <v>0.9592401281672432</v>
+        <v>0.9270210444649277</v>
       </c>
       <c r="E166" t="n">
-        <v>0.7362878740477158</v>
+        <v>0.7278373321570739</v>
       </c>
     </row>
     <row r="167">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.8915662650602411</v>
+        <v>0.8536585365853659</v>
       </c>
       <c r="C167" t="n">
-        <v>0.3750000000000001</v>
+        <v>0.4193548387096776</v>
       </c>
       <c r="D167" t="n">
-        <v>0.908477471644922</v>
+        <v>0.8770978510901344</v>
       </c>
       <c r="E167" t="n">
-        <v>0.7250145789017211</v>
+        <v>0.7167037421283927</v>
       </c>
     </row>
     <row r="168">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.9156626506024097</v>
+        <v>0.8414634146341462</v>
       </c>
       <c r="C168" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5161290322580646</v>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>0.9835733002093877</v>
       </c>
       <c r="E168" t="n">
-        <v>0.8052208835341365</v>
+        <v>0.7803885823671995</v>
       </c>
     </row>
     <row r="169">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.9277108433734942</v>
+        <v>0.8536585365853659</v>
       </c>
       <c r="C169" t="n">
-        <v>0.4999999999999999</v>
+        <v>0.5483870967741935</v>
       </c>
       <c r="D169" t="n">
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>0.8092369477911646</v>
+        <v>0.8006818777865199</v>
       </c>
     </row>
     <row r="170">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.9518072289156628</v>
+        <v>0.8780487804878049</v>
       </c>
       <c r="C170" t="n">
-        <v>0.53125</v>
+        <v>0.5806451612903227</v>
       </c>
       <c r="D170" t="n">
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>0.8276857429718877</v>
+        <v>0.8195646472593759</v>
       </c>
     </row>
     <row r="171">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.9397590361445783</v>
+        <v>0.8902439024390245</v>
       </c>
       <c r="C171" t="n">
-        <v>0.625</v>
+        <v>0.6774193548387097</v>
       </c>
       <c r="D171" t="n">
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>0.8549196787148595</v>
+        <v>0.8558877524259114</v>
       </c>
     </row>
     <row r="172">
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.9638554216867473</v>
+        <v>0.9024390243902438</v>
       </c>
       <c r="C172" t="n">
-        <v>0.6875</v>
+        <v>0.7419354838709679</v>
       </c>
       <c r="D172" t="n">
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>0.8837851405622491</v>
+        <v>0.8814581694204039</v>
       </c>
     </row>
     <row r="173">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.9518072289156628</v>
+        <v>0.9024390243902438</v>
       </c>
       <c r="C173" t="n">
-        <v>0.7187499999999999</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>0.8901857429718877</v>
+        <v>0.8922108575924469</v>
       </c>
     </row>
     <row r="174">
@@ -3447,16 +3447,16 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.9518072289156628</v>
+        <v>0.9146341463414634</v>
       </c>
       <c r="C174" t="n">
-        <v>0.78125</v>
+        <v>0.8387096774193549</v>
       </c>
       <c r="D174" t="n">
-        <v>0.9940035084602725</v>
+        <v>0.994697007603812</v>
       </c>
       <c r="E174" t="n">
-        <v>0.9090202457919784</v>
+        <v>0.9160136104548767</v>
       </c>
     </row>
     <row r="175">
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1</v>
+        <v>0.9512195121951221</v>
       </c>
       <c r="C175" t="n">
-        <v>0.8749999999999999</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="D175" t="n">
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.962234461054288</v>
       </c>
     </row>
     <row r="176">
@@ -3485,16 +3485,16 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>0.9756097560975611</v>
       </c>
       <c r="C176" t="n">
-        <v>0.84375</v>
+        <v>0.903225806451613</v>
       </c>
       <c r="D176" t="n">
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>0.9479166666666666</v>
+        <v>0.9596118541830579</v>
       </c>
     </row>
     <row r="177">
@@ -3504,16 +3504,16 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1</v>
+        <v>0.9878048780487804</v>
       </c>
       <c r="C177" t="n">
-        <v>0.8124999999999999</v>
+        <v>0.903225806451613</v>
       </c>
       <c r="D177" t="n">
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>0.9375</v>
+        <v>0.9636768948334645</v>
       </c>
     </row>
     <row r="178">
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.9673913043478261</v>
+        <v>0.9878048780487804</v>
       </c>
       <c r="C178" t="n">
-        <v>0.84375</v>
+        <v>0.903225806451613</v>
       </c>
       <c r="D178" t="n">
-        <v>0.9929551033202063</v>
+        <v>0.9926387329695173</v>
       </c>
       <c r="E178" t="n">
-        <v>0.9346988025560109</v>
+        <v>0.9612231391566369</v>
       </c>
     </row>
     <row r="179">
@@ -3542,16 +3542,16 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.9891304347826085</v>
+        <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>0.8749999999999999</v>
+        <v>0.9677419354838708</v>
       </c>
       <c r="D179" t="n">
-        <v>0.9262690029706721</v>
+        <v>0.9207868286683762</v>
       </c>
       <c r="E179" t="n">
-        <v>0.9301331459177602</v>
+        <v>0.9628429213840825</v>
       </c>
     </row>
     <row r="180">
@@ -3564,13 +3564,13 @@
         <v>1</v>
       </c>
       <c r="C180" t="n">
-        <v>0.9062500000000001</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>0.9922248499806769</v>
+        <v>0.9879257613712907</v>
       </c>
       <c r="E180" t="n">
-        <v>0.9661582833268924</v>
+        <v>0.9959752537904302</v>
       </c>
     </row>
     <row r="181">
@@ -3599,16 +3599,35 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.9684210526315788</v>
+        <v>0.9882352941176469</v>
       </c>
       <c r="C182" t="n">
-        <v>0.9375</v>
+        <v>0.9393939393939393</v>
       </c>
       <c r="D182" t="n">
-        <v>0.954831548220203</v>
+        <v>0.9534926259476181</v>
       </c>
       <c r="E182" t="n">
-        <v>0.9535842002839273</v>
+        <v>0.9603739531530681</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>0.9882352941176469</v>
+      </c>
+      <c r="C183" t="n">
+        <v>1</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.9712501816740463</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.986495158597231</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D182"/>
+  <dimension ref="A1:D183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3686,7 +3705,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="C4" t="n">
         <v>5.9</v>
@@ -3702,7 +3721,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="C5" t="n">
         <v>5.9</v>
@@ -3718,7 +3737,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="C6" t="n">
         <v>6.1</v>
@@ -3734,7 +3753,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="C7" t="n">
         <v>6.3</v>
@@ -3750,7 +3769,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="C8" t="n">
         <v>6.4</v>
@@ -3766,7 +3785,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="C9" t="n">
         <v>6.5</v>
@@ -3782,7 +3801,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="C10" t="n">
         <v>6.6</v>
@@ -3798,7 +3817,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="C11" t="n">
         <v>6.7</v>
@@ -3814,7 +3833,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="C12" t="n">
         <v>6.9</v>
@@ -3830,7 +3849,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
@@ -3846,7 +3865,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
@@ -3862,7 +3881,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="C15" t="n">
         <v>7.1</v>
@@ -3878,7 +3897,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="C16" t="n">
         <v>7.2</v>
@@ -3894,7 +3913,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
         <v>7.1</v>
@@ -3910,7 +3929,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="C18" t="n">
         <v>7.2</v>
@@ -3926,7 +3945,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="C19" t="n">
         <v>7.2</v>
@@ -3942,7 +3961,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="C20" t="n">
         <v>7.2</v>
@@ -3958,7 +3977,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="C21" t="n">
         <v>7.1</v>
@@ -3974,7 +3993,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="C22" t="n">
         <v>7</v>
@@ -3990,7 +4009,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="C23" t="n">
         <v>6.9</v>
@@ -4006,13 +4025,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="C24" t="n">
         <v>6.8</v>
       </c>
       <c r="D24" t="n">
-        <v>0.213931336725321</v>
+        <v>0.2105058800605199</v>
       </c>
     </row>
     <row r="25">
@@ -4022,13 +4041,13 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="C25" t="n">
         <v>6.7</v>
       </c>
       <c r="D25" t="n">
-        <v>0.2182484042507248</v>
+        <v>0.2146924625203246</v>
       </c>
     </row>
     <row r="26">
@@ -4038,13 +4057,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="C26" t="n">
         <v>6.6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.2181028585196967</v>
+        <v>0.214597665058659</v>
       </c>
     </row>
     <row r="27">
@@ -4054,13 +4073,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="C27" t="n">
         <v>6.5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2185958097911715</v>
+        <v>0.215024108630904</v>
       </c>
     </row>
     <row r="28">
@@ -4070,13 +4089,13 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="C28" t="n">
         <v>6.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2172222433013914</v>
+        <v>0.2136504283411237</v>
       </c>
     </row>
     <row r="29">
@@ -4086,13 +4105,13 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="C29" t="n">
         <v>6.3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.2178010163122744</v>
+        <v>0.2142377228564658</v>
       </c>
     </row>
     <row r="30">
@@ -4102,13 +4121,13 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="C30" t="n">
         <v>6.2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2160378170270998</v>
+        <v>0.2123923622042895</v>
       </c>
     </row>
     <row r="31">
@@ -4118,13 +4137,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="C31" t="n">
         <v>6.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2167167319171494</v>
+        <v>0.2130640498279781</v>
       </c>
     </row>
     <row r="32">
@@ -4134,13 +4153,13 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="C32" t="n">
         <v>6.1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2198416824131605</v>
+        <v>0.2161353832177457</v>
       </c>
     </row>
     <row r="33">
@@ -4150,13 +4169,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="C33" t="n">
         <v>5.9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.219139161584949</v>
+        <v>0.21538183222886</v>
       </c>
     </row>
     <row r="34">
@@ -4166,13 +4185,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="C34" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2187602876319878</v>
+        <v>0.2149883683635729</v>
       </c>
     </row>
     <row r="35">
@@ -4182,13 +4201,13 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="C35" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2119571588139313</v>
+        <v>0.2094029707921079</v>
       </c>
     </row>
     <row r="36">
@@ -4198,13 +4217,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="C36" t="n">
         <v>5.7</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2156662321708225</v>
+        <v>0.212483990941346</v>
       </c>
     </row>
     <row r="37">
@@ -4214,13 +4233,13 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="C37" t="n">
         <v>5.6</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2202994011171443</v>
+        <v>0.2201550262566146</v>
       </c>
     </row>
     <row r="38">
@@ -4230,13 +4249,13 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="C38" t="n">
         <v>5.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2224782495762383</v>
+        <v>0.2223286212692439</v>
       </c>
     </row>
     <row r="39">
@@ -4246,13 +4265,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="C39" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2254332403816362</v>
+        <v>0.2252691174230988</v>
       </c>
     </row>
     <row r="40">
@@ -4262,13 +4281,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="C40" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2249205544331556</v>
+        <v>0.2247622917189485</v>
       </c>
     </row>
     <row r="41">
@@ -4278,13 +4297,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="C41" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2274453362709764</v>
+        <v>0.2272836840920228</v>
       </c>
     </row>
     <row r="42">
@@ -4294,13 +4313,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="C42" t="n">
         <v>5.7</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2247464567387061</v>
+        <v>0.2245953528713353</v>
       </c>
     </row>
     <row r="43">
@@ -4310,13 +4329,13 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="C43" t="n">
         <v>5.7</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2248368217595582</v>
+        <v>0.2246822722198572</v>
       </c>
     </row>
     <row r="44">
@@ -4326,13 +4345,13 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="C44" t="n">
         <v>5.7</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2254800353761997</v>
+        <v>0.2253268412878366</v>
       </c>
     </row>
     <row r="45">
@@ -4342,13 +4361,13 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="C45" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D45" t="n">
-        <v>0.2239497540878107</v>
+        <v>0.2237965497733879</v>
       </c>
     </row>
     <row r="46">
@@ -4358,13 +4377,13 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="C46" t="n">
         <v>5.5</v>
       </c>
       <c r="D46" t="n">
-        <v>0.2223118384310669</v>
+        <v>0.2221579843811103</v>
       </c>
     </row>
     <row r="47">
@@ -4374,13 +4393,13 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="C47" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="D47" t="n">
-        <v>0.2146186410844288</v>
+        <v>0.2144646355987552</v>
       </c>
     </row>
     <row r="48">
@@ -4390,13 +4409,13 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="C48" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2186584209756129</v>
+        <v>0.2185021880640406</v>
       </c>
     </row>
     <row r="49">
@@ -4406,13 +4425,13 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="C49" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.2235432443611518</v>
+        <v>0.2233877085041337</v>
       </c>
     </row>
     <row r="50">
@@ -4422,13 +4441,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="C50" t="n">
         <v>5.2</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2230418541871345</v>
+        <v>0.2228885487332309</v>
       </c>
     </row>
     <row r="51">
@@ -4438,13 +4457,13 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="C51" t="n">
         <v>5.3</v>
       </c>
       <c r="D51" t="n">
-        <v>0.2261423795371857</v>
+        <v>0.2259952908372311</v>
       </c>
     </row>
     <row r="52">
@@ -4454,13 +4473,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="C52" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="D52" t="n">
-        <v>0.2264056574507284</v>
+        <v>0.2262598525427572</v>
       </c>
     </row>
     <row r="53">
@@ -4470,13 +4489,13 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="C53" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2270579781342783</v>
+        <v>0.2269161386168632</v>
       </c>
     </row>
     <row r="54">
@@ -4486,13 +4505,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="C54" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2256455764716248</v>
+        <v>0.2255116135295384</v>
       </c>
     </row>
     <row r="55">
@@ -4502,13 +4521,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="C55" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2269323866994425</v>
+        <v>0.2268025967635851</v>
       </c>
     </row>
     <row r="56">
@@ -4518,13 +4537,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="C56" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D56" t="n">
-        <v>0.2278941804780362</v>
+        <v>0.2277693945106953</v>
       </c>
     </row>
     <row r="57">
@@ -4534,13 +4553,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24.6</v>
+        <v>24.2</v>
       </c>
       <c r="C57" t="n">
         <v>5.8</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2287023027182463</v>
+        <v>0.2285807873414926</v>
       </c>
     </row>
     <row r="58">
@@ -4550,13 +4569,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="C58" t="n">
         <v>6</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2285970857885173</v>
+        <v>0.2284795893576861</v>
       </c>
     </row>
     <row r="59">
@@ -4566,13 +4585,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="C59" t="n">
         <v>6.2</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2213950728545218</v>
+        <v>0.2212833433084906</v>
       </c>
     </row>
     <row r="60">
@@ -4582,13 +4601,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="C60" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2251391808126245</v>
+        <v>0.2250271980703358</v>
       </c>
     </row>
     <row r="61">
@@ -4598,13 +4617,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="C61" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2291925040041381</v>
+        <v>0.2290960142036387</v>
       </c>
     </row>
     <row r="62">
@@ -4614,13 +4633,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="C62" t="n">
         <v>6.2</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2287022668226405</v>
+        <v>0.2286275552957955</v>
       </c>
     </row>
     <row r="63">
@@ -4630,13 +4649,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="C63" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2314413930807513</v>
+        <v>0.2313727950217048</v>
       </c>
     </row>
     <row r="64">
@@ -4646,13 +4665,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="C64" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2309385636370666</v>
+        <v>0.2308592502395401</v>
       </c>
     </row>
     <row r="65">
@@ -4662,13 +4681,13 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.3</v>
+        <v>24</v>
       </c>
       <c r="C65" t="n">
         <v>6.2</v>
       </c>
       <c r="D65" t="n">
-        <v>0.2300556887626649</v>
+        <v>0.2300833427047019</v>
       </c>
     </row>
     <row r="66">
@@ -4678,13 +4697,13 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="C66" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D66" t="n">
-        <v>0.2284906276059606</v>
+        <v>0.2285257396057603</v>
       </c>
     </row>
     <row r="67">
@@ -4694,13 +4713,13 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="C67" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2274648220144418</v>
+        <v>0.2274993688070017</v>
       </c>
     </row>
     <row r="68">
@@ -4710,13 +4729,13 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="C68" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2283736765590723</v>
+        <v>0.2284217922332903</v>
       </c>
     </row>
     <row r="69">
@@ -4726,13 +4745,13 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="C69" t="n">
         <v>6.2</v>
       </c>
       <c r="D69" t="n">
-        <v>0.227739378996592</v>
+        <v>0.227804503817838</v>
       </c>
     </row>
     <row r="70">
@@ -4742,13 +4761,13 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="C70" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2245297737927425</v>
+        <v>0.2246004883263343</v>
       </c>
     </row>
     <row r="71">
@@ -4758,13 +4777,13 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="C71" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2153118724187444</v>
+        <v>0.2153890943542398</v>
       </c>
     </row>
     <row r="72">
@@ -4774,13 +4793,13 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2181368107409092</v>
+        <v>0.2182218956649522</v>
       </c>
     </row>
     <row r="73">
@@ -4790,13 +4809,13 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="C73" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2205197880620159</v>
+        <v>0.2206122234126222</v>
       </c>
     </row>
     <row r="74">
@@ -4806,13 +4825,13 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="C74" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2186286523599865</v>
+        <v>0.2187313336330215</v>
       </c>
     </row>
     <row r="75">
@@ -4822,13 +4841,13 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="C75" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2200929417920177</v>
+        <v>0.2202060009178136</v>
       </c>
     </row>
     <row r="76">
@@ -4838,13 +4857,13 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="C76" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2191753307115642</v>
+        <v>0.2194252358311471</v>
       </c>
     </row>
     <row r="77">
@@ -4854,13 +4873,13 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="C77" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2175911308009368</v>
+        <v>0.2178468890771772</v>
       </c>
     </row>
     <row r="78">
@@ -4870,13 +4889,13 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="C78" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2161574089217935</v>
+        <v>0.2164068169510294</v>
       </c>
     </row>
     <row r="79">
@@ -4886,13 +4905,13 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="C79" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2146095360080125</v>
+        <v>0.2148510715648591</v>
       </c>
     </row>
     <row r="80">
@@ -4902,13 +4921,13 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="C80" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2135497203635996</v>
+        <v>0.2137409175460669</v>
       </c>
     </row>
     <row r="81">
@@ -4918,13 +4937,13 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="C81" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2135914700576878</v>
+        <v>0.2137765128655618</v>
       </c>
     </row>
     <row r="82">
@@ -4934,13 +4953,13 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="C82" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2112552108545566</v>
+        <v>0.2114835031238878</v>
       </c>
     </row>
     <row r="83">
@@ -4950,13 +4969,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="C83" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2027358661530098</v>
+        <v>0.2030377503203539</v>
       </c>
     </row>
     <row r="84">
@@ -4966,13 +4985,13 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="C84" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="D84" t="n">
-        <v>0.2048076210931714</v>
+        <v>0.2056436362623874</v>
       </c>
     </row>
     <row r="85">
@@ -4982,13 +5001,13 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="C85" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="D85" t="n">
-        <v>0.209548828152231</v>
+        <v>0.2104230801933988</v>
       </c>
     </row>
     <row r="86">
@@ -4998,13 +5017,13 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="C86" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2077211610594956</v>
+        <v>0.208667212909856</v>
       </c>
     </row>
     <row r="87">
@@ -5014,13 +5033,13 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="C87" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="D87" t="n">
-        <v>0.2087065635519888</v>
+        <v>0.2096811934655787</v>
       </c>
     </row>
     <row r="88">
@@ -5030,13 +5049,13 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="C88" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D88" t="n">
-        <v>0.2070763939707692</v>
+        <v>0.2081073803542761</v>
       </c>
     </row>
     <row r="89">
@@ -5046,13 +5065,13 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="C89" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2077623512441399</v>
+        <v>0.2088539270466073</v>
       </c>
     </row>
     <row r="90">
@@ -5062,13 +5081,13 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="C90" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D90" t="n">
-        <v>0.2053325653510505</v>
+        <v>0.2064769212507251</v>
       </c>
     </row>
     <row r="91">
@@ -5078,13 +5097,13 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="C91" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D91" t="n">
-        <v>0.203835660478318</v>
+        <v>0.2050179116447231</v>
       </c>
     </row>
     <row r="92">
@@ -5094,13 +5113,13 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="C92" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2032500016506408</v>
+        <v>0.204474536745659</v>
       </c>
     </row>
     <row r="93">
@@ -5110,13 +5129,13 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="C93" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D93" t="n">
-        <v>0.2041420759579269</v>
+        <v>0.2054379317545111</v>
       </c>
     </row>
     <row r="94">
@@ -5126,13 +5145,13 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>22.7</v>
+        <v>22.3</v>
       </c>
       <c r="C94" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2029127923881969</v>
+        <v>0.2035408750291889</v>
       </c>
     </row>
     <row r="95">
@@ -5142,13 +5161,13 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="C95" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D95" t="n">
-        <v>0.1981407541124788</v>
+        <v>0.1987779985246286</v>
       </c>
     </row>
     <row r="96">
@@ -5158,13 +5177,13 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="C96" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D96" t="n">
-        <v>0.2022693830179685</v>
+        <v>0.2029309496048711</v>
       </c>
     </row>
     <row r="97">
@@ -5174,13 +5193,13 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="C97" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D97" t="n">
-        <v>0.2062953440577102</v>
+        <v>0.2069862542990786</v>
       </c>
     </row>
     <row r="98">
@@ -5190,13 +5209,13 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="C98" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2058670578992161</v>
+        <v>0.2066115786935035</v>
       </c>
     </row>
     <row r="99">
@@ -5206,13 +5225,13 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="C99" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2076469989939749</v>
+        <v>0.2084221002065939</v>
       </c>
     </row>
     <row r="100">
@@ -5222,13 +5241,13 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="C100" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D100" t="n">
-        <v>0.2078155673487014</v>
+        <v>0.2086194017281998</v>
       </c>
     </row>
     <row r="101">
@@ -5238,13 +5257,13 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="C101" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D101" t="n">
-        <v>0.2098398540641272</v>
+        <v>0.210677075136139</v>
       </c>
     </row>
     <row r="102">
@@ -5254,13 +5273,13 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="C102" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2076659636631001</v>
+        <v>0.2085232061794116</v>
       </c>
     </row>
     <row r="103">
@@ -5270,13 +5289,13 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="C103" t="n">
         <v>4.9</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2074831131473929</v>
+        <v>0.2083683707733407</v>
       </c>
     </row>
     <row r="104">
@@ -5286,13 +5305,13 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D104" t="n">
-        <v>0.2074963541975982</v>
+        <v>0.2084117181672706</v>
       </c>
     </row>
     <row r="105">
@@ -5302,13 +5321,13 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>23.9</v>
+        <v>23.5</v>
       </c>
       <c r="C105" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D105" t="n">
-        <v>0.2061406116457954</v>
+        <v>0.2070701391631624</v>
       </c>
     </row>
     <row r="106">
@@ -5318,13 +5337,13 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="C106" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D106" t="n">
-        <v>0.2047406984123495</v>
+        <v>0.2056514741084033</v>
       </c>
     </row>
     <row r="107">
@@ -5334,13 +5353,13 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D107" t="n">
-        <v>0.19896653835297</v>
+        <v>0.1998604286423448</v>
       </c>
     </row>
     <row r="108">
@@ -5350,13 +5369,13 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="C108" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="D108" t="n">
-        <v>0.2015906344128766</v>
+        <v>0.2025051244822138</v>
       </c>
     </row>
     <row r="109">
@@ -5366,13 +5385,13 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="C109" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2049617222126288</v>
+        <v>0.2059033280858125</v>
       </c>
     </row>
     <row r="110">
@@ -5382,13 +5401,13 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="C110" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="D110" t="n">
-        <v>0.2063049191642995</v>
+        <v>0.2072814996790829</v>
       </c>
     </row>
     <row r="111">
@@ -5398,13 +5417,13 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="C111" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2124041829488596</v>
+        <v>0.2134343979859439</v>
       </c>
     </row>
     <row r="112">
@@ -5414,13 +5433,13 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="C112" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2086829309096993</v>
+        <v>0.2097233441768734</v>
       </c>
     </row>
     <row r="113">
@@ -5433,10 +5452,10 @@
         <v>20.5</v>
       </c>
       <c r="C113" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="D113" t="n">
-        <v>0.2037288037575383</v>
+        <v>0.2047744326914384</v>
       </c>
     </row>
     <row r="114">
@@ -5446,13 +5465,13 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="C114" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="D114" t="n">
-        <v>0.1987019944069678</v>
+        <v>0.1997521408054976</v>
       </c>
     </row>
     <row r="115">
@@ -5462,13 +5481,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="C115" t="n">
         <v>4.9</v>
       </c>
       <c r="D115" t="n">
-        <v>0.1940492012785181</v>
+        <v>0.195092288385341</v>
       </c>
     </row>
     <row r="116">
@@ -5478,13 +5497,13 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="C116" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1915773012585851</v>
+        <v>0.1926571603789215</v>
       </c>
     </row>
     <row r="117">
@@ -5494,13 +5513,13 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>21</v>
+        <v>20.5</v>
       </c>
       <c r="C117" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="D117" t="n">
-        <v>0.1900961997935539</v>
+        <v>0.1912005200489418</v>
       </c>
     </row>
     <row r="118">
@@ -5510,13 +5529,13 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>21.8</v>
+        <v>21.3</v>
       </c>
       <c r="C118" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1854385185013807</v>
+        <v>0.1865992586106102</v>
       </c>
     </row>
     <row r="119">
@@ -5526,13 +5545,13 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>22.5</v>
+        <v>21.8</v>
       </c>
       <c r="C119" t="n">
         <v>4.2</v>
       </c>
       <c r="D119" t="n">
-        <v>0.1818803610654994</v>
+        <v>0.1831479712166515</v>
       </c>
     </row>
     <row r="120">
@@ -5542,13 +5561,13 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="C120" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D120" t="n">
-        <v>0.1858714557327593</v>
+        <v>0.1872144749013558</v>
       </c>
     </row>
     <row r="121">
@@ -5558,13 +5577,13 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="C121" t="n">
         <v>4.1</v>
       </c>
       <c r="D121" t="n">
-        <v>0.1904600509602341</v>
+        <v>0.1918170911426083</v>
       </c>
     </row>
     <row r="122">
@@ -5574,13 +5593,13 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="C122" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D122" t="n">
-        <v>0.1925534957116604</v>
+        <v>0.1938963875423917</v>
       </c>
     </row>
     <row r="123">
@@ -5590,13 +5609,13 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D123" t="n">
-        <v>0.194199271170299</v>
+        <v>0.1955841182065099</v>
       </c>
     </row>
     <row r="124">
@@ -5606,13 +5625,13 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="C124" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D124" t="n">
-        <v>0.1944966162606</v>
+        <v>0.1957894428410273</v>
       </c>
     </row>
     <row r="125">
@@ -5622,13 +5641,13 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1958304068444608</v>
+        <v>0.1971948145699181</v>
       </c>
     </row>
     <row r="126">
@@ -5638,13 +5657,13 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="C126" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D126" t="n">
-        <v>0.1961475664806731</v>
+        <v>0.1976667113514158</v>
       </c>
     </row>
     <row r="127">
@@ -5654,13 +5673,13 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="C127" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="D127" t="n">
-        <v>0.1995627355981759</v>
+        <v>0.2010126928436566</v>
       </c>
     </row>
     <row r="128">
@@ -5670,13 +5689,13 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>25</v>
+        <v>24.5</v>
       </c>
       <c r="C128" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="D128" t="n">
-        <v>0.2033843640109402</v>
+        <v>0.2048551774359981</v>
       </c>
     </row>
     <row r="129">
@@ -5686,13 +5705,13 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>25.8</v>
+        <v>25.2</v>
       </c>
       <c r="C129" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2072054832890305</v>
+        <v>0.2086919585814299</v>
       </c>
     </row>
     <row r="130">
@@ -5702,13 +5721,13 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>26.1</v>
+        <v>25.5</v>
       </c>
       <c r="C130" t="n">
         <v>4.3</v>
       </c>
       <c r="D130" t="n">
-        <v>0.2077732597443219</v>
+        <v>0.2092380124476215</v>
       </c>
     </row>
     <row r="131">
@@ -5718,13 +5737,13 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
       <c r="C131" t="n">
         <v>4.4</v>
       </c>
       <c r="D131" t="n">
-        <v>0.2073371391083059</v>
+        <v>0.2087277699243423</v>
       </c>
     </row>
     <row r="132">
@@ -5734,13 +5753,13 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>26.7</v>
+        <v>26</v>
       </c>
       <c r="C132" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="D132" t="n">
-        <v>0.2160652662084651</v>
+        <v>0.2174850750035563</v>
       </c>
     </row>
     <row r="133">
@@ -5750,13 +5769,13 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>26.2</v>
+        <v>25.6</v>
       </c>
       <c r="C133" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="D133" t="n">
-        <v>0.2215273748379286</v>
+        <v>0.2228509719785166</v>
       </c>
     </row>
     <row r="134">
@@ -5766,13 +5785,13 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>25.9</v>
+        <v>25.4</v>
       </c>
       <c r="C134" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2218743896975197</v>
+        <v>0.2232934460129385</v>
       </c>
     </row>
     <row r="135">
@@ -5782,13 +5801,13 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="C135" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D135" t="n">
-        <v>0.2230346650151756</v>
+        <v>0.224466607514054</v>
       </c>
     </row>
     <row r="136">
@@ -5798,13 +5817,13 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="C136" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="D136" t="n">
-        <v>0.2236469469438087</v>
+        <v>0.2250776158334455</v>
       </c>
     </row>
     <row r="137">
@@ -5814,13 +5833,13 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="C137" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="D137" t="n">
-        <v>0.2246118042112892</v>
+        <v>0.2261939343407518</v>
       </c>
     </row>
     <row r="138">
@@ -5830,13 +5849,13 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>26.9</v>
+        <v>26.5</v>
       </c>
       <c r="C138" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D138" t="n">
-        <v>0.2253502634844697</v>
+        <v>0.2269412326058056</v>
       </c>
     </row>
     <row r="139">
@@ -5846,13 +5865,13 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
       <c r="C139" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D139" t="n">
-        <v>0.2255393188876454</v>
+        <v>0.2271080482955739</v>
       </c>
     </row>
     <row r="140">
@@ -5862,13 +5881,13 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="C140" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="D140" t="n">
-        <v>0.2280493677485341</v>
+        <v>0.2295316544408021</v>
       </c>
     </row>
     <row r="141">
@@ -5878,13 +5897,13 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>27.7</v>
+        <v>27.2</v>
       </c>
       <c r="C141" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="D141" t="n">
-        <v>0.2286391414654763</v>
+        <v>0.2302160465261997</v>
       </c>
     </row>
     <row r="142">
@@ -5894,13 +5913,13 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="C142" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2281753404173369</v>
+        <v>0.2297498347237704</v>
       </c>
     </row>
     <row r="143">
@@ -5910,13 +5929,13 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="C143" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="D143" t="n">
-        <v>0.2257120628881144</v>
+        <v>0.2271226287507213</v>
       </c>
     </row>
     <row r="144">
@@ -5926,13 +5945,13 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>28</v>
+        <v>27.7</v>
       </c>
       <c r="C144" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="D144" t="n">
-        <v>0.2282672486775731</v>
+        <v>0.2296623005084529</v>
       </c>
     </row>
     <row r="145">
@@ -5942,13 +5961,13 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>28.1</v>
+        <v>27.7</v>
       </c>
       <c r="C145" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2321667275627601</v>
+        <v>0.2337491979196922</v>
       </c>
     </row>
     <row r="146">
@@ -5958,13 +5977,13 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>28.1</v>
+        <v>27.7</v>
       </c>
       <c r="C146" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2298259181428325</v>
+        <v>0.231401365204684</v>
       </c>
     </row>
     <row r="147">
@@ -5974,13 +5993,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="C147" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D147" t="n">
-        <v>0.2328904567233725</v>
+        <v>0.2344587233260903</v>
       </c>
     </row>
     <row r="148">
@@ -5990,13 +6009,13 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>28.4</v>
+        <v>28</v>
       </c>
       <c r="C148" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="D148" t="n">
-        <v>0.232253119485672</v>
+        <v>0.2337935444507051</v>
       </c>
     </row>
     <row r="149">
@@ -6006,13 +6025,13 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>28.2</v>
+        <v>27.8</v>
       </c>
       <c r="C149" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="D149" t="n">
-        <v>0.2297956207643675</v>
+        <v>0.2313817636993311</v>
       </c>
     </row>
     <row r="150">
@@ -6022,13 +6041,13 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>27.8</v>
+        <v>27.3</v>
       </c>
       <c r="C150" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="D150" t="n">
-        <v>0.2276890592092407</v>
+        <v>0.229288359236466</v>
       </c>
     </row>
     <row r="151">
@@ -6038,13 +6057,13 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>27.3</v>
+        <v>26.9</v>
       </c>
       <c r="C151" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="D151" t="n">
-        <v>0.2280235151110713</v>
+        <v>0.2296181638858062</v>
       </c>
     </row>
     <row r="152">
@@ -6054,13 +6073,13 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>27.3</v>
+        <v>26.8</v>
       </c>
       <c r="C152" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="D152" t="n">
-        <v>0.2260629917884326</v>
+        <v>0.2276679765581801</v>
       </c>
     </row>
     <row r="153">
@@ -6070,13 +6089,13 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>27.4</v>
+        <v>26.8</v>
       </c>
       <c r="C153" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="D153" t="n">
-        <v>0.2265726951791928</v>
+        <v>0.22818312215479</v>
       </c>
     </row>
     <row r="154">
@@ -6086,13 +6105,13 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="C154" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="D154" t="n">
-        <v>0.2257207196371064</v>
+        <v>0.2273303699795831</v>
       </c>
     </row>
     <row r="155">
@@ -6102,13 +6121,13 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>26.3</v>
+        <v>25.8</v>
       </c>
       <c r="C155" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D155" t="n">
-        <v>0.2207881384697674</v>
+        <v>0.2223982205270898</v>
       </c>
     </row>
     <row r="156">
@@ -6118,13 +6137,13 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>26.2</v>
+        <v>25.7</v>
       </c>
       <c r="C156" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="D156" t="n">
-        <v>0.2253823067762058</v>
+        <v>0.2269996991041931</v>
       </c>
     </row>
     <row r="157">
@@ -6134,13 +6153,13 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>26.2</v>
+        <v>25.8</v>
       </c>
       <c r="C157" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="D157" t="n">
-        <v>0.2291800617182597</v>
+        <v>0.2307998998903195</v>
       </c>
     </row>
     <row r="158">
@@ -6150,13 +6169,13 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>26.4</v>
+        <v>26.1</v>
       </c>
       <c r="C158" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="D158" t="n">
-        <v>0.2309754226259297</v>
+        <v>0.2309106224989629</v>
       </c>
     </row>
     <row r="159">
@@ -6166,13 +6185,13 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>26.5</v>
+        <v>26.1</v>
       </c>
       <c r="C159" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2314148940180176</v>
+        <v>0.2313516735410197</v>
       </c>
     </row>
     <row r="160">
@@ -6182,13 +6201,13 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>26.5</v>
+        <v>26</v>
       </c>
       <c r="C160" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="D160" t="n">
-        <v>0.2304735908828276</v>
+        <v>0.2306294483365661</v>
       </c>
     </row>
     <row r="161">
@@ -6198,13 +6217,13 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>26.8</v>
+        <v>26.4</v>
       </c>
       <c r="C161" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="D161" t="n">
-        <v>0.2295633119176595</v>
+        <v>0.2294983172850124</v>
       </c>
     </row>
     <row r="162">
@@ -6214,13 +6233,13 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>27</v>
+        <v>26.5</v>
       </c>
       <c r="C162" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="D162" t="n">
-        <v>0.2287346795503076</v>
+        <v>0.2287026976988926</v>
       </c>
     </row>
     <row r="163">
@@ -6230,13 +6249,13 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="C163" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="D163" t="n">
-        <v>0.2298570558348192</v>
+        <v>0.2297852499560769</v>
       </c>
     </row>
     <row r="164">
@@ -6246,13 +6265,13 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>27.2</v>
+        <v>26.5</v>
       </c>
       <c r="C164" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D164" t="n">
-        <v>0.2319892207870588</v>
+        <v>0.2319214393587778</v>
       </c>
     </row>
     <row r="165">
@@ -6262,13 +6281,13 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>27.2</v>
+        <v>26.4</v>
       </c>
       <c r="C165" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="D165" t="n">
-        <v>0.2320964832863319</v>
+        <v>0.2320130487636571</v>
       </c>
     </row>
     <row r="166">
@@ -6278,13 +6297,13 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>27.1</v>
+        <v>26.4</v>
       </c>
       <c r="C166" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="D166" t="n">
-        <v>0.2308112917621809</v>
+        <v>0.2307141182294245</v>
       </c>
     </row>
     <row r="167">
@@ -6294,13 +6313,13 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>27.5</v>
+        <v>26.8</v>
       </c>
       <c r="C167" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="D167" t="n">
-        <v>0.2282218837971295</v>
+        <v>0.2281525216296589</v>
       </c>
     </row>
     <row r="168">
@@ -6310,13 +6329,13 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>27.7</v>
+        <v>26.7</v>
       </c>
       <c r="C168" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="D168" t="n">
-        <v>0.2339722417843579</v>
+        <v>0.2336158570051581</v>
       </c>
     </row>
     <row r="169">
@@ -6326,13 +6345,13 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>27.8</v>
+        <v>26.8</v>
       </c>
       <c r="C169" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="D169" t="n">
-        <v>0.2377756997320589</v>
+        <v>0.2378872739647667</v>
       </c>
     </row>
     <row r="170">
@@ -6342,13 +6361,13 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C170" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="D170" t="n">
-        <v>0.2398621869369248</v>
+        <v>0.2399049316696376</v>
       </c>
     </row>
     <row r="171">
@@ -6358,13 +6377,13 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>27.9</v>
+        <v>27.1</v>
       </c>
       <c r="C171" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="D171" t="n">
-        <v>0.2419560898912403</v>
+        <v>0.242166066134934</v>
       </c>
     </row>
     <row r="172">
@@ -6374,13 +6393,13 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>28.1</v>
+        <v>27.2</v>
       </c>
       <c r="C172" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="D172" t="n">
-        <v>0.2426468029894171</v>
+        <v>0.2426195938894051</v>
       </c>
     </row>
     <row r="173">
@@ -6390,13 +6409,13 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>28</v>
+        <v>27.2</v>
       </c>
       <c r="C173" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="D173" t="n">
-        <v>0.2436848819483159</v>
+        <v>0.243827945819321</v>
       </c>
     </row>
     <row r="174">
@@ -6406,13 +6425,13 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>28</v>
+        <v>27.3</v>
       </c>
       <c r="C174" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="D174" t="n">
-        <v>0.2433142716617252</v>
+        <v>0.2435061603754021</v>
       </c>
     </row>
     <row r="175">
@@ -6422,13 +6441,13 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>28.6</v>
+        <v>27.6</v>
       </c>
       <c r="C175" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="D175" t="n">
-        <v>0.2445324170963497</v>
+        <v>0.2446972358539269</v>
       </c>
     </row>
     <row r="176">
@@ -6438,13 +6457,13 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>28.8</v>
+        <v>27.8</v>
       </c>
       <c r="C176" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="D176" t="n">
-        <v>0.2458421710504727</v>
+        <v>0.2461147734487857</v>
       </c>
     </row>
     <row r="177">
@@ -6454,13 +6473,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>29.3</v>
+        <v>27.9</v>
       </c>
       <c r="C177" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="D177" t="n">
-        <v>0.2479227732342474</v>
+        <v>0.2481374902754657</v>
       </c>
     </row>
     <row r="178">
@@ -6470,13 +6489,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>29</v>
+        <v>27.9</v>
       </c>
       <c r="C178" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="D178" t="n">
-        <v>0.2474575112640342</v>
+        <v>0.2476590850714911</v>
       </c>
     </row>
     <row r="179">
@@ -6486,13 +6505,13 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>29.2</v>
+        <v>28.1</v>
       </c>
       <c r="C179" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="D179" t="n">
-        <v>0.2430534003388238</v>
+        <v>0.2429894643675</v>
       </c>
     </row>
     <row r="180">
@@ -6502,13 +6521,13 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>29.5</v>
+        <v>28.3</v>
       </c>
       <c r="C180" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="D180" t="n">
-        <v>0.2474092835719974</v>
+        <v>0.2473527913139845</v>
       </c>
     </row>
     <row r="181">
@@ -6518,13 +6537,13 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>29.6</v>
+        <v>28.3</v>
       </c>
       <c r="C181" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="D181" t="n">
-        <v>0.2514723625654082</v>
+        <v>0.2514689798394417</v>
       </c>
     </row>
     <row r="182">
@@ -6534,13 +6553,29 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>29.3</v>
+        <v>28.2</v>
       </c>
       <c r="C182" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2483289996014</v>
+        <v>0.2482915491357856</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="C183" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.2495047632536906</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed/idc_data.xlsx
+++ b/data/processed/idc_data.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E183"/>
+  <dimension ref="A1:E184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3605,10 +3605,10 @@
         <v>0.9393939393939393</v>
       </c>
       <c r="D182" t="n">
-        <v>0.9534926259476181</v>
+        <v>0.9532678679451505</v>
       </c>
       <c r="E182" t="n">
-        <v>0.9603739531530681</v>
+        <v>0.9602990338189121</v>
       </c>
     </row>
     <row r="183">
@@ -3618,16 +3618,35 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.9882352941176469</v>
+        <v>1</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>0.9712501816740463</v>
+        <v>0.9710636030967117</v>
       </c>
       <c r="E183" t="n">
-        <v>0.986495158597231</v>
+        <v>0.9903545343655705</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.9436946533708811</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.981231551123627</v>
       </c>
     </row>
   </sheetData>
@@ -3641,7 +3660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D183"/>
+  <dimension ref="A1:D184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6521,7 +6540,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="C180" t="n">
         <v>7.2</v>
@@ -6543,7 +6562,7 @@
         <v>7.4</v>
       </c>
       <c r="D181" t="n">
-        <v>0.2514689798394417</v>
+        <v>0.2514593636361441</v>
       </c>
     </row>
     <row r="182">
@@ -6559,7 +6578,7 @@
         <v>7.2</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2482915491357856</v>
+        <v>0.2482670266247457</v>
       </c>
     </row>
     <row r="183">
@@ -6569,13 +6588,29 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>28.2</v>
+        <v>28.4</v>
       </c>
       <c r="C183" t="n">
         <v>7.4</v>
       </c>
       <c r="D183" t="n">
-        <v>0.2495047632536906</v>
+        <v>0.2494826780720774</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="C184" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.2476130670072468</v>
       </c>
     </row>
   </sheetData>
